--- a/output/yearly_surface_area_iteration_88_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_88_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497652015344</v>
+        <v>10.8449764891652</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907259677647</v>
+        <v>37.78907248879867</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.214642894331557</v>
+        <v>3.406664533736432</v>
       </c>
       <c r="C2" t="n">
-        <v>7.162831250184728</v>
+        <v>9.647634689633405</v>
       </c>
       <c r="D2" t="n">
-        <v>19.47100221832699</v>
+        <v>24.45631706049229</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.21218067730433</v>
+        <v>13.63156687346696</v>
       </c>
       <c r="C3" t="n">
-        <v>20.67069791291659</v>
+        <v>20.6854241284803</v>
       </c>
       <c r="D3" t="n">
-        <v>65.53656799699583</v>
+        <v>93.90907664972866</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.07195498651306</v>
+        <v>29.35425635697963</v>
       </c>
       <c r="C4" t="n">
-        <v>64.65594030628644</v>
+        <v>63.44348189154163</v>
       </c>
       <c r="D4" t="n">
-        <v>93.25719617410877</v>
+        <v>116.5619231775195</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.27053006467818</v>
+        <v>36.37375244234433</v>
       </c>
       <c r="C5" t="n">
-        <v>116.7052583423396</v>
+        <v>115.5271610972434</v>
       </c>
       <c r="D5" t="n">
-        <v>76.23270923476484</v>
+        <v>82.95768100885549</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.11202671593793</v>
+        <v>33.12711278440013</v>
       </c>
       <c r="C6" t="n">
-        <v>158.4305175205333</v>
+        <v>141.122305494662</v>
       </c>
       <c r="D6" t="n">
-        <v>52.48815925985148</v>
+        <v>54.13847715069036</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.852943133008</v>
+        <v>23.29589127407256</v>
       </c>
       <c r="C7" t="n">
-        <v>147.8001533789488</v>
+        <v>120.6715190674967</v>
       </c>
       <c r="D7" t="n">
-        <v>40.54323494228053</v>
+        <v>40.72289477215769</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.60073178400781</v>
+        <v>12.51728322914683</v>
       </c>
       <c r="C8" t="n">
-        <v>91.20927046304992</v>
+        <v>80.36095833112266</v>
       </c>
       <c r="D8" t="n">
-        <v>35.9663271450819</v>
+        <v>36.21667280966483</v>
       </c>
     </row>
     <row r="9">
@@ -881,10 +881,10 @@
         <v>6.878124415953151</v>
       </c>
       <c r="C9" t="n">
-        <v>47.48124596819272</v>
+        <v>44.48593372253571</v>
       </c>
       <c r="D9" t="n">
-        <v>33.39218466454675</v>
+        <v>34.16874709860598</v>
       </c>
     </row>
     <row r="10">
@@ -895,10 +895,10 @@
         <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>31.17539834835747</v>
+        <v>30.60598467989432</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>34.87658719336794</v>
       </c>
     </row>
     <row r="11">
@@ -909,7 +909,7 @@
         <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>28.78680618392497</v>
+        <v>28.96450251839364</v>
       </c>
       <c r="D11" t="n">
         <v>35.7169632282032</v>
@@ -926,7 +926,7 @@
         <v>27.12078032981814</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>34.93156506480576</v>
       </c>
     </row>
     <row r="13">
@@ -940,7 +940,7 @@
         <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>32.26022956155019</v>
+        <v>32.00006641992479</v>
       </c>
     </row>
     <row r="14">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -982,7 +982,7 @@
         <v>19.01252604044373</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -993,10 +993,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1007,7 +1007,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -1021,7 +1021,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
         <v>16.24890625298896</v>
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.651330077840826</v>
+        <v>7.658859791753085</v>
       </c>
       <c r="C21" t="n">
-        <v>92.77237719382001</v>
+        <v>92.86367497500616</v>
       </c>
       <c r="D21" t="n">
-        <v>7.651330077840826</v>
+        <v>7.658859791753085</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.452045912310037</v>
+        <v>5.310273332270997</v>
       </c>
       <c r="C2" t="n">
-        <v>5.535093556543517</v>
+        <v>8.035604959260143</v>
       </c>
       <c r="D2" t="n">
-        <v>18.36948129416207</v>
+        <v>26.12332466230338</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.51513980728909</v>
+        <v>12.55164439879547</v>
       </c>
       <c r="C3" t="n">
-        <v>24.06754496961056</v>
+        <v>29.03518835309941</v>
       </c>
       <c r="D3" t="n">
-        <v>65.30585728649783</v>
+        <v>91.45470738911162</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.702596865538</v>
+        <v>27.32498385230147</v>
       </c>
       <c r="C4" t="n">
-        <v>57.66196966123216</v>
+        <v>57.5726306201457</v>
       </c>
       <c r="D4" t="n">
-        <v>101.3742861928214</v>
+        <v>133.8426462676719</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.19752088166541</v>
+        <v>39.58897617375263</v>
       </c>
       <c r="C5" t="n">
-        <v>116.5825398793088</v>
+        <v>114.9381124746953</v>
       </c>
       <c r="D5" t="n">
-        <v>89.73174016815848</v>
+        <v>101.3163630782709</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>46.49066253460771</v>
+        <v>40.21140421824511</v>
       </c>
       <c r="C6" t="n">
-        <v>171.4318023678738</v>
+        <v>161.0871268082252</v>
       </c>
       <c r="D6" t="n">
-        <v>61.70578845502478</v>
+        <v>65.97246397768143</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>33.77604801690726</v>
+        <v>30.84160412891355</v>
       </c>
       <c r="C7" t="n">
-        <v>184.1513256240954</v>
+        <v>157.9209904620292</v>
       </c>
       <c r="D7" t="n">
-        <v>45.63359678880023</v>
+        <v>45.75337000871835</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>18.85937339858123</v>
+        <v>18.10833640483241</v>
       </c>
       <c r="C8" t="n">
-        <v>139.4425351726957</v>
+        <v>117.2452195796753</v>
       </c>
       <c r="D8" t="n">
-        <v>38.05254101660637</v>
+        <v>38.80357801035517</v>
       </c>
     </row>
     <row r="9">
@@ -1192,10 +1192,10 @@
         <v>9.429686699290611</v>
       </c>
       <c r="C9" t="n">
-        <v>76.54686850012379</v>
+        <v>69.0031191406913</v>
       </c>
       <c r="D9" t="n">
-        <v>34.94530953266521</v>
+        <v>35.72187196672443</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.121196935978863</v>
+        <v>5.978843518863076</v>
       </c>
       <c r="C10" t="n">
-        <v>42.70602513473626</v>
+        <v>40.85543071223102</v>
       </c>
       <c r="D10" t="n">
-        <v>35.01894061048373</v>
+        <v>35.3036474447153</v>
       </c>
     </row>
     <row r="11">
@@ -1217,10 +1217,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
-        <v>32.16303653882975</v>
+        <v>31.98534020436108</v>
       </c>
       <c r="D11" t="n">
         <v>36.25005223160922</v>
@@ -1237,7 +1237,7 @@
         <v>29.94134148411922</v>
       </c>
       <c r="D12" t="n">
-        <v>35.36549755008285</v>
+        <v>35.1485313074443</v>
       </c>
     </row>
     <row r="13">
@@ -1251,7 +1251,7 @@
         <v>27.57729301229291</v>
       </c>
       <c r="D13" t="n">
-        <v>33.04071898642641</v>
+        <v>32.780555844801</v>
       </c>
     </row>
     <row r="14">
@@ -1262,7 +1262,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>25.19753657719863</v>
       </c>
       <c r="D14" t="n">
         <v>30.42141611149592</v>
@@ -1276,7 +1276,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.21695054710532</v>
+        <v>22.57528845915541</v>
       </c>
       <c r="D15" t="n">
         <v>29.38370878810703</v>
@@ -1293,7 +1293,7 @@
         <v>20.25247339090745</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>18.88882582970863</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1318,7 +1318,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -1332,7 +1332,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
         <v>16.24890625298896</v>
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.824885428720213</v>
+        <v>7.833297151273187</v>
       </c>
       <c r="C21" t="n">
-        <v>100.7453998947727</v>
+        <v>100.8537008226423</v>
       </c>
       <c r="D21" t="n">
-        <v>8.802996107310239</v>
+        <v>8.812459295182334</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.86085386790421</v>
+        <v>6.021058670145687</v>
       </c>
       <c r="C2" t="n">
-        <v>9.644689446520665</v>
+        <v>16.13502351929633</v>
       </c>
       <c r="D2" t="n">
-        <v>23.7622214335898</v>
+        <v>28.13688920371359</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.33766445699867</v>
+        <v>14.59367962362884</v>
       </c>
       <c r="C3" t="n">
-        <v>22.67837196810132</v>
+        <v>29.75186417719959</v>
       </c>
       <c r="D3" t="n">
-        <v>64.30938336668731</v>
+        <v>90.29624509810039</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.17557827480671</v>
+        <v>25.18084686622644</v>
       </c>
       <c r="C4" t="n">
-        <v>57.98103766511237</v>
+        <v>63.37966829076559</v>
       </c>
       <c r="D4" t="n">
-        <v>107.1685611432861</v>
+        <v>143.4529745445439</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.02571503342222</v>
+        <v>39.88350048502668</v>
       </c>
       <c r="C5" t="n">
-        <v>110.6675099612217</v>
+        <v>109.6857622569749</v>
       </c>
       <c r="D5" t="n">
-        <v>102.1508486268806</v>
+        <v>120.7058802371454</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>53.7762122478233</v>
+        <v>45.88688769649593</v>
       </c>
       <c r="C6" t="n">
-        <v>177.8720673077329</v>
+        <v>170.7072725621397</v>
       </c>
       <c r="D6" t="n">
-        <v>71.76870242355459</v>
+        <v>77.92720577229484</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>42.27994663109313</v>
+        <v>37.60879105428681</v>
       </c>
       <c r="C7" t="n">
-        <v>210.0223411264074</v>
+        <v>188.3433883212293</v>
       </c>
       <c r="D7" t="n">
-        <v>51.50248456478767</v>
+        <v>52.46067032413256</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>25.86905200690345</v>
+        <v>24.20008090968387</v>
       </c>
       <c r="C8" t="n">
-        <v>182.7523351455437</v>
+        <v>155.2977605962817</v>
       </c>
       <c r="D8" t="n">
-        <v>40.47254910757476</v>
+        <v>41.14013754646259</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>13.20156137900685</v>
+        <v>12.97968639784708</v>
       </c>
       <c r="C9" t="n">
-        <v>117.0390525617834</v>
+        <v>101.2859288994392</v>
       </c>
       <c r="D9" t="n">
-        <v>36.49843440078366</v>
+        <v>37.27499683484289</v>
       </c>
     </row>
     <row r="10">
@@ -1517,10 +1517,10 @@
         <v>7.260024272905163</v>
       </c>
       <c r="C10" t="n">
-        <v>61.78138302825178</v>
+        <v>57.22607368054658</v>
       </c>
       <c r="D10" t="n">
-        <v>35.44600086183109</v>
+        <v>35.73070769606267</v>
       </c>
     </row>
     <row r="11">
@@ -1531,10 +1531,10 @@
         <v>5.153193699591506</v>
       </c>
       <c r="C11" t="n">
-        <v>38.91549724863931</v>
+        <v>38.02701557629594</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>36.78314123501524</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>32.97886888105885</v>
+        <v>32.76190263842031</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>35.36549755008285</v>
       </c>
     </row>
     <row r="13">
@@ -1562,7 +1562,7 @@
         <v>29.65859814529614</v>
       </c>
       <c r="D13" t="n">
-        <v>33.56104526967722</v>
+        <v>33.30088212805181</v>
       </c>
     </row>
     <row r="14">
@@ -1573,7 +1573,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>27.3485457972034</v>
+        <v>27.04125876577415</v>
       </c>
       <c r="D14" t="n">
         <v>30.42141611149592</v>
@@ -1604,7 +1604,7 @@
         <v>21.49242074137117</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -1618,7 +1618,7 @@
         <v>19.36104647545135</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1629,7 +1629,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -1643,7 +1643,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
         <v>16.24890625298896</v>
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.983925048179177</v>
+        <v>7.992493163213184</v>
       </c>
       <c r="C21" t="n">
-        <v>108.7809787814413</v>
+        <v>108.8977193487796</v>
       </c>
       <c r="D21" t="n">
-        <v>9.979906310223971</v>
+        <v>9.990616454016481</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.063674732055801</v>
+        <v>5.468334712654734</v>
       </c>
       <c r="C2" t="n">
-        <v>6.634650985299944</v>
+        <v>11.10062129191869</v>
       </c>
       <c r="D2" t="n">
-        <v>19.62710010330223</v>
+        <v>23.37541283811655</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.48907458763093</v>
+        <v>17.45056544298705</v>
       </c>
       <c r="C3" t="n">
-        <v>36.37375244234433</v>
+        <v>47.88965301315941</v>
       </c>
       <c r="D3" t="n">
-        <v>71.30924449796707</v>
+        <v>99.29887154604364</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.59001467471911</v>
+        <v>19.15684295296801</v>
       </c>
       <c r="C4" t="n">
-        <v>86.96517513759096</v>
+        <v>88.81576956009619</v>
       </c>
       <c r="D4" t="n">
-        <v>106.6708150572329</v>
+        <v>137.0205635863188</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.2869166760141</v>
+        <v>25.84450831429729</v>
       </c>
       <c r="C5" t="n">
-        <v>106.2741889847172</v>
+        <v>102.0035864712436</v>
       </c>
       <c r="D5" t="n">
-        <v>70.34222300928397</v>
+        <v>79.00614649926207</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>26.24407962992574</v>
+        <v>23.34596040698915</v>
       </c>
       <c r="C6" t="n">
-        <v>138.3046895834737</v>
+        <v>124.0556034040355</v>
       </c>
       <c r="D6" t="n">
-        <v>33.89189424600839</v>
+        <v>34.5359207399943</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.12757044828985</v>
+        <v>15.9897248590678</v>
       </c>
       <c r="C7" t="n">
-        <v>128.516664972133</v>
+        <v>109.1732899553581</v>
       </c>
       <c r="D7" t="n">
-        <v>28.44613973055133</v>
+        <v>28.92523261022377</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.095892479846697</v>
+        <v>9.012443924985718</v>
       </c>
       <c r="C8" t="n">
-        <v>86.20235717139117</v>
+        <v>74.60300804571511</v>
       </c>
       <c r="D8" t="n">
-        <v>26.8704346652352</v>
+        <v>27.45457454926205</v>
       </c>
     </row>
     <row r="9">
@@ -1814,10 +1814,10 @@
         <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>47.14843349645305</v>
+        <v>43.59843379789659</v>
       </c>
       <c r="D9" t="n">
-        <v>27.06874770149305</v>
+        <v>27.17968519207294</v>
       </c>
     </row>
     <row r="10">
@@ -1828,10 +1828,10 @@
         <v>3.701188845010476</v>
       </c>
       <c r="C10" t="n">
-        <v>30.46363126277853</v>
+        <v>29.75186417719959</v>
       </c>
       <c r="D10" t="n">
-        <v>28.61303684027329</v>
+        <v>28.75539025738908</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>26.29905750136355</v>
+        <v>26.12136116689488</v>
       </c>
       <c r="D11" t="n">
-        <v>28.43141351498762</v>
+        <v>28.25371718051895</v>
       </c>
     </row>
     <row r="12">
@@ -1859,7 +1859,7 @@
         <v>24.0832529328785</v>
       </c>
       <c r="D12" t="n">
-        <v>27.33774657245668</v>
+        <v>27.12078032981814</v>
       </c>
     </row>
     <row r="13">
@@ -1870,7 +1870,7 @@
         <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
-        <v>22.63419332141022</v>
+        <v>22.37403017978481</v>
       </c>
       <c r="D13" t="n">
         <v>25.23582473766426</v>
@@ -1901,7 +1901,7 @@
         <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
-        <v>21.85861263505523</v>
+        <v>22.21695054710532</v>
       </c>
     </row>
     <row r="16">
@@ -1915,7 +1915,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>20.25247339090745</v>
+        <v>20.66578917439536</v>
       </c>
     </row>
     <row r="17">
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.58328130950962</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
         <v>17.9443845382232</v>
@@ -1940,7 +1940,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>15.51652246562084</v>
+        <v>16.05157496443535</v>
       </c>
       <c r="D18" t="n">
         <v>13.9113649691773</v>
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
       <c r="D19" t="n">
         <v>9.027170140549421</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.199916678767854</v>
+        <v>3.353650157707104</v>
       </c>
       <c r="C2" t="n">
-        <v>3.269219855141878</v>
+        <v>4.929355223023235</v>
       </c>
       <c r="D2" t="n">
-        <v>14.10967800543516</v>
+        <v>16.97245431101886</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.82072538521711</v>
+        <v>18.49121800948867</v>
       </c>
       <c r="C3" t="n">
-        <v>31.69081589308704</v>
+        <v>46.56429361242621</v>
       </c>
       <c r="D3" t="n">
-        <v>71.5301377314226</v>
+        <v>96.92304210176636</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.86476516318797</v>
+        <v>25.15532142591602</v>
       </c>
       <c r="C4" t="n">
-        <v>91.99368687874312</v>
+        <v>105.6242720045058</v>
       </c>
       <c r="D4" t="n">
-        <v>115.7833972480518</v>
+        <v>151.6083527237222</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.57577148524092</v>
+        <v>28.29887757491431</v>
       </c>
       <c r="C5" t="n">
-        <v>133.7385810110218</v>
+        <v>132.5113963807133</v>
       </c>
       <c r="D5" t="n">
-        <v>86.36925428111316</v>
+        <v>101.8808680082128</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.47679489356124</v>
+        <v>27.85414586489051</v>
       </c>
       <c r="C6" t="n">
-        <v>157.4644777795544</v>
+        <v>144.9462128027034</v>
       </c>
       <c r="D6" t="n">
-        <v>42.2642386678252</v>
+        <v>43.31078172055229</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.92983824910874</v>
+        <v>15.03153909972291</v>
       </c>
       <c r="C7" t="n">
-        <v>160.1966816404733</v>
+        <v>138.6973886651724</v>
       </c>
       <c r="D7" t="n">
-        <v>31.56024344842221</v>
+        <v>31.62013005838127</v>
       </c>
     </row>
     <row r="8">
@@ -2111,10 +2111,10 @@
         <v>7.760715602071035</v>
       </c>
       <c r="C8" t="n">
-        <v>112.7389976171825</v>
+        <v>97.30101496790137</v>
       </c>
       <c r="D8" t="n">
-        <v>27.62147165898401</v>
+        <v>28.20561154301086</v>
       </c>
     </row>
     <row r="9">
@@ -2125,10 +2125,10 @@
         <v>4.437499623195581</v>
       </c>
       <c r="C9" t="n">
-        <v>52.58437053486764</v>
+        <v>48.8124958551514</v>
       </c>
       <c r="D9" t="n">
-        <v>28.06718511671205</v>
+        <v>28.17812260729194</v>
       </c>
     </row>
     <row r="10">
@@ -2139,7 +2139,7 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>32.45657910239955</v>
+        <v>32.17187226816798</v>
       </c>
       <c r="D10" t="n">
         <v>29.89421759431538</v>
@@ -2153,10 +2153,10 @@
         <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>28.96450251839364</v>
+        <v>28.78680618392497</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>29.31989518733098</v>
       </c>
     </row>
     <row r="12">
@@ -2167,7 +2167,7 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>20.82875929330033</v>
+        <v>20.39482680802324</v>
       </c>
       <c r="D12" t="n">
         <v>28.20561154301086</v>
@@ -2198,7 +2198,7 @@
         <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
-        <v>18.12993485432585</v>
+        <v>18.4372218857551</v>
       </c>
     </row>
     <row r="15">
@@ -2212,7 +2212,7 @@
         <v>13.97517856995334</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -2223,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.22610507161303</v>
+        <v>13.63942085510094</v>
       </c>
       <c r="D16" t="n">
         <v>15.29268398905256</v>
@@ -2237,7 +2237,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.22217808079604</v>
+        <v>13.69439872653876</v>
       </c>
       <c r="D17" t="n">
         <v>11.8055161435679</v>
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>13.9113649691773</v>
+        <v>14.44641746799181</v>
       </c>
       <c r="D18" t="n">
         <v>7.490734983403163</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.923464736797754</v>
+        <v>3.314380249537232</v>
       </c>
       <c r="C2" t="n">
-        <v>10.42321537598839</v>
+        <v>5.725552611167398</v>
       </c>
       <c r="D2" t="n">
-        <v>15.15622105816226</v>
+        <v>17.51732428687584</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.52557917913731</v>
+        <v>14.92747384307275</v>
       </c>
       <c r="C3" t="n">
-        <v>21.57390580082366</v>
+        <v>32.40258297866598</v>
       </c>
       <c r="D3" t="n">
-        <v>66.58703804053992</v>
+        <v>88.76471867947537</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.50137964389641</v>
+        <v>30.08173140582652</v>
       </c>
       <c r="C4" t="n">
-        <v>85.3698351181899</v>
+        <v>110.8314618278309</v>
       </c>
       <c r="D4" t="n">
-        <v>123.7090464644363</v>
+        <v>163.3755807068245</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.43542262126263</v>
+        <v>32.64311116620645</v>
       </c>
       <c r="C5" t="n">
-        <v>152.5390495473482</v>
+        <v>162.2828955119978</v>
       </c>
       <c r="D5" t="n">
-        <v>104.65430527271</v>
+        <v>127.8971821707532</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.07806645691679</v>
+        <v>32.48308629041422</v>
       </c>
       <c r="C6" t="n">
-        <v>183.2657891948649</v>
+        <v>176.906027566754</v>
       </c>
       <c r="D6" t="n">
-        <v>55.99005332089985</v>
+        <v>60.53849043467533</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.25407703341745</v>
+        <v>22.21793229480956</v>
       </c>
       <c r="C7" t="n">
-        <v>193.6134099976262</v>
+        <v>172.4135500721206</v>
       </c>
       <c r="D7" t="n">
-        <v>35.51275970571987</v>
+        <v>35.75230614555609</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.34900346109313</v>
+        <v>10.84831213192725</v>
       </c>
       <c r="C8" t="n">
-        <v>158.135011461555</v>
+        <v>135.7707987588126</v>
       </c>
       <c r="D8" t="n">
-        <v>29.37389131106456</v>
+        <v>29.87458264023044</v>
       </c>
     </row>
     <row r="9">
@@ -2436,10 +2436,10 @@
         <v>5.546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>89.30467991681108</v>
+        <v>78.4328058399819</v>
       </c>
       <c r="D9" t="n">
-        <v>29.06562253193106</v>
+        <v>29.17656002251095</v>
       </c>
     </row>
     <row r="10">
@@ -2447,10 +2447,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.562361508084175</v>
+        <v>2.704714925199962</v>
       </c>
       <c r="C10" t="n">
-        <v>44.98367980858886</v>
+        <v>42.84837855185204</v>
       </c>
       <c r="D10" t="n">
         <v>30.17892442854695</v>
@@ -2464,10 +2464,10 @@
         <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>32.87382187670443</v>
+        <v>32.51842920776709</v>
       </c>
       <c r="D11" t="n">
-        <v>30.20837685967435</v>
+        <v>29.852984190737</v>
       </c>
     </row>
     <row r="12">
@@ -2478,7 +2478,7 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>25.16808414607123</v>
+        <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
         <v>28.63954402828795</v>
@@ -2492,7 +2492,7 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>18.73174619702914</v>
       </c>
       <c r="D13" t="n">
         <v>26.53664044579129</v>
@@ -2509,7 +2509,7 @@
         <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>19.0517959486136</v>
       </c>
     </row>
     <row r="15">
@@ -2523,7 +2523,7 @@
         <v>15.40853021815369</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.05273663858884</v>
+        <v>14.46605242207675</v>
       </c>
       <c r="D16" t="n">
         <v>14.87936820556466</v>
@@ -2548,7 +2548,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.16661937228147</v>
+        <v>14.63884001802419</v>
       </c>
       <c r="D17" t="n">
         <v>10.86107485208246</v>
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.89026524130261</v>
+        <v>1.971349390127595</v>
       </c>
       <c r="C2" t="n">
-        <v>4.85081540668349</v>
+        <v>2.727295122397639</v>
       </c>
       <c r="D2" t="n">
-        <v>10.58324025178061</v>
+        <v>12.2335581426195</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.43860454408685</v>
+        <v>14.7753029489145</v>
       </c>
       <c r="C3" t="n">
-        <v>31.17539834835747</v>
+        <v>30.2280118137593</v>
       </c>
       <c r="D3" t="n">
-        <v>66.04707680320416</v>
+        <v>86.64905237682348</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.12599216797563</v>
+        <v>33.22136056400782</v>
       </c>
       <c r="C4" t="n">
-        <v>82.23020596000859</v>
+        <v>110.7421227867444</v>
       </c>
       <c r="D4" t="n">
-        <v>130.6774916691802</v>
+        <v>172.7051291402819</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.42346172236243</v>
+        <v>34.23845118560752</v>
       </c>
       <c r="C5" t="n">
-        <v>180.3470532701391</v>
+        <v>198.8529974951915</v>
       </c>
       <c r="D5" t="n">
-        <v>109.980286568249</v>
+        <v>134.5730665596316</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.51075515258238</v>
+        <v>26.68684784454105</v>
       </c>
       <c r="C6" t="n">
-        <v>222.9136702308723</v>
+        <v>210.6369151892659</v>
       </c>
       <c r="D6" t="n">
-        <v>54.66174867705392</v>
+        <v>58.68691426446584</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.485826244881928</v>
+        <v>7.186393195086651</v>
       </c>
       <c r="C7" t="n">
-        <v>203.8540203006247</v>
+        <v>180.0191495369206</v>
       </c>
       <c r="D7" t="n">
-        <v>35.15344004596554</v>
+        <v>35.51275970571987</v>
       </c>
     </row>
     <row r="8">
@@ -2733,10 +2733,10 @@
         <v>3.838633523605028</v>
       </c>
       <c r="C8" t="n">
-        <v>113.8238288303752</v>
+        <v>97.71825774220626</v>
       </c>
       <c r="D8" t="n">
-        <v>31.04286240828414</v>
+        <v>31.37665662772806</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>34.27968458918587</v>
+        <v>32.61562223048752</v>
       </c>
       <c r="D9" t="n">
-        <v>31.50624732468863</v>
+        <v>31.61718481526852</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>25.76596849795754</v>
+        <v>25.48126166372597</v>
       </c>
       <c r="D10" t="n">
-        <v>23.63066724122073</v>
+        <v>23.34596040698915</v>
       </c>
     </row>
     <row r="11">
@@ -2775,7 +2775,7 @@
         <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>20.07968579496001</v>
+        <v>19.72429312602266</v>
       </c>
       <c r="D11" t="n">
         <v>22.92282714645877</v>
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.4046032273367</v>
+        <v>15.18763698469816</v>
       </c>
       <c r="D12" t="n">
         <v>21.47965802121596</v>
@@ -2806,7 +2806,7 @@
         <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
-        <v>15.34962535589888</v>
+        <v>15.60978849752428</v>
       </c>
     </row>
     <row r="14">
@@ -2820,7 +2820,7 @@
         <v>12.90605532002857</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>14.74977750860408</v>
       </c>
     </row>
     <row r="15">
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>11.82515109765283</v>
+        <v>12.18348900970292</v>
       </c>
       <c r="D15" t="n">
         <v>12.541826921753</v>
@@ -2845,7 +2845,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>11.98615772114931</v>
+        <v>12.39947350463721</v>
       </c>
       <c r="D16" t="n">
         <v>9.092947236733956</v>
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.27768003604838</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.992367002544278</v>
+        <v>2.701769682087222</v>
       </c>
       <c r="C2" t="n">
-        <v>5.720643872646163</v>
+        <v>6.516841260790327</v>
       </c>
       <c r="D2" t="n">
-        <v>11.84085906092078</v>
+        <v>17.06081160440107</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.83911654969054</v>
+        <v>10.9563043793944</v>
       </c>
       <c r="C3" t="n">
-        <v>24.96093538047515</v>
+        <v>20.43507846389736</v>
       </c>
       <c r="D3" t="n">
-        <v>60.45602362751859</v>
+        <v>78.19129590473722</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.67104207028186</v>
+        <v>30.83473189498382</v>
       </c>
       <c r="C4" t="n">
-        <v>79.95844177238148</v>
+        <v>93.6145523384546</v>
       </c>
       <c r="D4" t="n">
-        <v>133.0003067374281</v>
+        <v>175.525690294583</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.06284151973436</v>
+        <v>40.86524818927349</v>
       </c>
       <c r="C5" t="n">
-        <v>168.2961002005095</v>
+        <v>202.8536193899972</v>
       </c>
       <c r="D5" t="n">
-        <v>126.9645218517188</v>
+        <v>158.9204096249524</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.17115256237099</v>
+        <v>34.29441080474959</v>
       </c>
       <c r="C6" t="n">
-        <v>253.7866902863218</v>
+        <v>258.4558823677196</v>
       </c>
       <c r="D6" t="n">
-        <v>70.84291433844986</v>
+        <v>80.26180181299375</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.76825078853552</v>
+        <v>14.73210604992764</v>
       </c>
       <c r="C7" t="n">
-        <v>259.0694746828738</v>
+        <v>235.7136967988422</v>
       </c>
       <c r="D7" t="n">
-        <v>40.96244121199391</v>
+        <v>41.20198765183014</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.006913291658733</v>
+        <v>4.923464736797754</v>
       </c>
       <c r="C8" t="n">
-        <v>177.661973299024</v>
+        <v>153.5453409442011</v>
       </c>
       <c r="D8" t="n">
-        <v>32.96217917008666</v>
+        <v>33.29597338953057</v>
       </c>
     </row>
     <row r="9">
@@ -3058,10 +3058,10 @@
         <v>2.218749811597791</v>
       </c>
       <c r="C9" t="n">
-        <v>73.1078062921472</v>
+        <v>64.01093206459626</v>
       </c>
       <c r="D9" t="n">
-        <v>32.28280975874785</v>
+        <v>32.39374724932775</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>31.74481201682062</v>
+        <v>30.7483380970101</v>
       </c>
       <c r="D10" t="n">
-        <v>24.76949457814703</v>
+        <v>24.62714116103124</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
+        <v>22.92282714645877</v>
+      </c>
+      <c r="D11" t="n">
         <v>23.63361248433346</v>
-      </c>
-      <c r="D11" t="n">
-        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>15.34962535589888</v>
+        <v>15.08946221427348</v>
       </c>
       <c r="D13" t="n">
-        <v>15.34962535589888</v>
+        <v>15.60978849752428</v>
       </c>
     </row>
     <row r="14">
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.90016483380309</v>
+        <v>13.25850274585317</v>
       </c>
       <c r="D15" t="n">
         <v>11.82515109765283</v>
@@ -3156,7 +3156,7 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.1456838753228</v>
+        <v>23.97231544229862</v>
       </c>
       <c r="D16" t="n">
         <v>8.266315669758143</v>
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.52766584773283</v>
+        <v>33.99988649347554</v>
       </c>
       <c r="D17" t="n">
         <v>4.249985811684442</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.012582793705961</v>
+        <v>1.721003725544659</v>
       </c>
       <c r="C2" t="n">
-        <v>2.900082718345077</v>
+        <v>3.372303364087794</v>
       </c>
       <c r="D2" t="n">
-        <v>8.656069508344128</v>
+        <v>12.48292205949819</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.03760951239764</v>
+        <v>10.29853341754904</v>
       </c>
       <c r="C3" t="n">
-        <v>24.19517217116264</v>
+        <v>23.04161861867264</v>
       </c>
       <c r="D3" t="n">
-        <v>57.01499792413352</v>
+        <v>75.54057710327082</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.22510762837556</v>
+        <v>27.52918737478481</v>
       </c>
       <c r="C4" t="n">
-        <v>73.75575977695013</v>
+        <v>78.42691535375644</v>
       </c>
       <c r="D4" t="n">
-        <v>133.4725273831709</v>
+        <v>175.3342494922549</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>53.99612373357458</v>
+        <v>44.32590884674349</v>
       </c>
       <c r="C5" t="n">
-        <v>165.9399057103171</v>
+        <v>196.5704340828177</v>
       </c>
       <c r="D5" t="n">
-        <v>140.3653780146877</v>
+        <v>176.0028196788469</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>47.21519234034186</v>
+        <v>39.92964262712628</v>
       </c>
       <c r="C6" t="n">
-        <v>271.2961605915636</v>
+        <v>291.5024918403715</v>
       </c>
       <c r="D6" t="n">
-        <v>83.24042434767857</v>
+        <v>94.71214627180255</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.69029180927252</v>
+        <v>13.29482741091031</v>
       </c>
       <c r="C7" t="n">
-        <v>305.721143840978</v>
+        <v>286.7370884839574</v>
       </c>
       <c r="D7" t="n">
-        <v>46.59178254814513</v>
+        <v>46.47200932822701</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.088979188187965</v>
+        <v>4.005530633326986</v>
       </c>
       <c r="C8" t="n">
-        <v>224.6435096857551</v>
+        <v>195.5199640392735</v>
       </c>
       <c r="D8" t="n">
-        <v>33.96356182841841</v>
+        <v>34.54770171244525</v>
       </c>
     </row>
     <row r="9">
@@ -3369,10 +3369,10 @@
         <v>1.664062358698343</v>
       </c>
       <c r="C9" t="n">
-        <v>84.86718029361549</v>
+        <v>72.33124385808797</v>
       </c>
       <c r="D9" t="n">
-        <v>32.17187226816797</v>
+        <v>31.94999728700819</v>
       </c>
     </row>
     <row r="10">
@@ -3383,7 +3383,7 @@
         <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>32.31422568528377</v>
+        <v>31.17539834835747</v>
       </c>
       <c r="D10" t="n">
         <v>25.33890824661018</v>
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.10052348092744</v>
+        <v>22.7451308119901</v>
       </c>
       <c r="D11" t="n">
-        <v>24.34439782220815</v>
+        <v>23.81130881880213</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.14033316844506</v>
+        <v>16.70640068316797</v>
       </c>
       <c r="D12" t="n">
-        <v>19.7439280801076</v>
+        <v>19.96089432274615</v>
       </c>
     </row>
     <row r="13">
@@ -3428,7 +3428,7 @@
         <v>11.18701508989241</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>10.75504610002381</v>
+        <v>11.06233313145306</v>
       </c>
       <c r="D14" t="n">
         <v>11.06233313145306</v>
@@ -3453,7 +3453,7 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>20.0669230748048</v>
       </c>
       <c r="D15" t="n">
         <v>6.808420328951629</v>
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.51878906066559</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
         <v>3.306526267903257</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.345215338996383</v>
+        <v>2.14217349066654</v>
       </c>
       <c r="C2" t="n">
-        <v>8.143597206727291</v>
+        <v>15.17683775995144</v>
       </c>
       <c r="D2" t="n">
-        <v>9.520007488081321</v>
+        <v>22.36813969355933</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.08745766113598</v>
+        <v>8.177958376375932</v>
       </c>
       <c r="C3" t="n">
-        <v>18.22614612934204</v>
+        <v>18.40776945462769</v>
       </c>
       <c r="D3" t="n">
-        <v>51.71356032120074</v>
+        <v>69.85134915716056</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.19659588722339</v>
+        <v>23.68760860806704</v>
       </c>
       <c r="C4" t="n">
-        <v>67.62965410245002</v>
+        <v>69.14841780091984</v>
       </c>
       <c r="D4" t="n">
-        <v>131.5325939195792</v>
+        <v>171.1480772813465</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>54.04521111878692</v>
+        <v>43.54051068334605</v>
       </c>
       <c r="C5" t="n">
-        <v>152.7599427808037</v>
+        <v>174.4565670446582</v>
       </c>
       <c r="D5" t="n">
-        <v>151.7291076913446</v>
+        <v>192.299831569344</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>56.75483478250812</v>
+        <v>47.05418571684538</v>
       </c>
       <c r="C6" t="n">
-        <v>269.3238294537318</v>
+        <v>300.6396177237966</v>
       </c>
       <c r="D6" t="n">
-        <v>99.66309994431923</v>
+        <v>117.6958417759246</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>29.04500583014188</v>
+        <v>24.13430381349934</v>
       </c>
       <c r="C7" t="n">
-        <v>342.0124294761656</v>
+        <v>339.8565115176395</v>
       </c>
       <c r="D7" t="n">
-        <v>55.93409370175777</v>
+        <v>57.07193929097983</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.927612711792993</v>
+        <v>7.009678608322226</v>
       </c>
       <c r="C8" t="n">
-        <v>297.7444437439726</v>
+        <v>267.2857212197154</v>
       </c>
       <c r="D8" t="n">
-        <v>37.55184968744049</v>
+        <v>37.38495257771854</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>2.218749811597791</v>
       </c>
       <c r="C9" t="n">
-        <v>153.8702994343068</v>
+        <v>131.7937388089088</v>
       </c>
       <c r="D9" t="n">
-        <v>33.05937219280708</v>
+        <v>32.9484347022272</v>
       </c>
     </row>
     <row r="10">
@@ -3694,10 +3694,10 @@
         <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>56.08724634362028</v>
+        <v>48.9695754878309</v>
       </c>
       <c r="D10" t="n">
-        <v>26.47773558353648</v>
+        <v>26.33538216642069</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>27.72062817711293</v>
+        <v>27.00984283923824</v>
       </c>
       <c r="D11" t="n">
-        <v>24.87748682561417</v>
+        <v>24.34439782220815</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>19.30999559483051</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>20.39482680802324</v>
       </c>
     </row>
     <row r="13">
@@ -3736,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>13.00815708127024</v>
       </c>
       <c r="D13" t="n">
         <v>16.65044106402591</v>
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="D14" t="n">
-        <v>11.36962016288231</v>
+        <v>11.06233313145306</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
         <v>6.450082416901544</v>
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>27.69215749368978</v>
+        <v>27.27884171020187</v>
       </c>
       <c r="D16" t="n">
         <v>2.89321048441535</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.535674393620264</v>
+        <v>4.41982816451914</v>
       </c>
       <c r="C2" t="n">
-        <v>10.29362467902781</v>
+        <v>8.420450059324892</v>
       </c>
       <c r="D2" t="n">
-        <v>16.83010089390307</v>
+        <v>19.43173231015712</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.104286240828415</v>
+        <v>1.54821612959722</v>
       </c>
       <c r="C2" t="n">
-        <v>4.625013434706723</v>
+        <v>8.86420002164445</v>
       </c>
       <c r="D2" t="n">
-        <v>7.006733365209485</v>
+        <v>16.64258708239193</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.16661937228147</v>
+        <v>10.84831213192725</v>
       </c>
       <c r="C3" t="n">
-        <v>25.01493150420873</v>
+        <v>32.47130531796326</v>
       </c>
       <c r="D3" t="n">
-        <v>56.08724634362028</v>
+        <v>77.73969196078369</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.38950146334128</v>
+        <v>32.80019079888594</v>
       </c>
       <c r="C4" t="n">
-        <v>94.32926466714628</v>
+        <v>100.123539617611</v>
       </c>
       <c r="D4" t="n">
-        <v>136.356902138248</v>
+        <v>176.7891995899486</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.45305302221007</v>
+        <v>27.29258617806133</v>
       </c>
       <c r="C5" t="n">
-        <v>228.4526907782328</v>
+        <v>256.0398012675682</v>
       </c>
       <c r="D5" t="n">
-        <v>139.0154749213484</v>
+        <v>174.3093048890212</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>18.03274183160542</v>
+        <v>14.97361598517235</v>
       </c>
       <c r="C6" t="n">
-        <v>278.0584387784157</v>
+        <v>279.8295116368769</v>
       </c>
       <c r="D6" t="n">
-        <v>80.86557665110554</v>
+        <v>89.19766941704822</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.210135066437822</v>
+        <v>4.611268966847268</v>
       </c>
       <c r="C7" t="n">
-        <v>209.3635884168578</v>
+        <v>187.9241820515159</v>
       </c>
       <c r="D7" t="n">
-        <v>33.47661496711198</v>
+        <v>33.53650157707104</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.585522542358599</v>
+        <v>1.50207398749762</v>
       </c>
       <c r="C8" t="n">
-        <v>113.4065860560703</v>
+        <v>97.13411785817941</v>
       </c>
       <c r="D8" t="n">
-        <v>24.36697801940583</v>
+        <v>24.28352946454485</v>
       </c>
     </row>
     <row r="9">
@@ -4302,10 +4302,10 @@
         <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>42.82187136383736</v>
+        <v>37.38593432542277</v>
       </c>
       <c r="D9" t="n">
-        <v>20.1906232855399</v>
+        <v>20.07968579496001</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>21.6377194015997</v>
+        <v>21.06830573313655</v>
       </c>
       <c r="D10" t="n">
-        <v>19.50241814486289</v>
+        <v>19.07535789351553</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.99267010218054</v>
+        <v>15.45958109877452</v>
       </c>
       <c r="D11" t="n">
-        <v>15.99267010218054</v>
+        <v>16.34806277111788</v>
       </c>
     </row>
     <row r="12">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.365873098514571</v>
+        <v>9.626036240139976</v>
       </c>
       <c r="D13" t="n">
-        <v>9.365873098514571</v>
+        <v>9.105709956889166</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>16.59349969717959</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
         <v>5.223879534297279</v>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>23.29196428325557</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
         <v>2.150027472300515</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.049529353568845</v>
+        <v>5.481097432809942</v>
       </c>
       <c r="C2" t="n">
-        <v>7.227626598665018</v>
+        <v>7.420049148697394</v>
       </c>
       <c r="D2" t="n">
-        <v>24.79207477534471</v>
+        <v>23.58157985600839</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.64076245570368</v>
+        <v>9.395325529641976</v>
       </c>
       <c r="C3" t="n">
-        <v>25.93777434620073</v>
+        <v>21.21556788877357</v>
       </c>
       <c r="D3" t="n">
-        <v>17.27385085622263</v>
+        <v>19.45823949817178</v>
       </c>
     </row>
     <row r="4">
@@ -4616,7 +4616,7 @@
         <v>22.74218556887735</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>39.60468413702056</v>
       </c>
     </row>
     <row r="10">
@@ -4630,7 +4630,7 @@
         <v>25.62361508084176</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>50.1084028247572</v>
       </c>
     </row>
     <row r="11">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.3965695272832</v>
+        <v>13.39646475635912</v>
       </c>
       <c r="C21" t="n">
-        <v>70.13498164283558</v>
+        <v>70.13443313623307</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576067003209788</v>
+        <v>1.576054677218721</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.757549374780043</v>
+        <v>4.122358610132356</v>
       </c>
       <c r="C2" t="n">
-        <v>10.04229726674062</v>
+        <v>5.723589115758905</v>
       </c>
       <c r="D2" t="n">
-        <v>23.29687302177681</v>
+        <v>24.79207477534471</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.36573422979433</v>
+        <v>15.09927969131594</v>
       </c>
       <c r="C3" t="n">
-        <v>27.34167356327367</v>
+        <v>26.04576659366788</v>
       </c>
       <c r="D3" t="n">
-        <v>33.92429192024854</v>
+        <v>34.56242792800896</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>11.32053277766997</v>
+        <v>11.03975293425538</v>
       </c>
       <c r="C4" t="n">
-        <v>40.0749412873548</v>
+        <v>32.8895298399724</v>
       </c>
       <c r="D4" t="n">
-        <v>24.12154109334413</v>
+        <v>25.2701859073129</v>
       </c>
     </row>
     <row r="5">
@@ -4882,7 +4882,7 @@
         <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.50317890838889</v>
+        <v>16.34217228489241</v>
       </c>
       <c r="D6" t="n">
         <v>34.57617239586842</v>
@@ -4896,7 +4896,7 @@
         <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>24.07441720354028</v>
+        <v>24.3139636433765</v>
       </c>
       <c r="D7" t="n">
         <v>34.97378021608837</v>
@@ -4913,7 +4913,7 @@
         <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.96770980341364</v>
+        <v>36.63391558396972</v>
       </c>
     </row>
     <row r="9">
@@ -4927,7 +4927,7 @@
         <v>25.73749781453438</v>
       </c>
       <c r="D9" t="n">
-        <v>39.82655911818034</v>
+        <v>40.60312155223957</v>
       </c>
     </row>
     <row r="10">
@@ -4941,7 +4941,7 @@
         <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>49.68134257340984</v>
       </c>
     </row>
     <row r="11">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43541505587901</v>
+        <v>15.43616541195399</v>
       </c>
       <c r="C21" t="n">
-        <v>86.11336820648293</v>
+        <v>86.11755440353278</v>
       </c>
       <c r="D21" t="n">
-        <v>3.249561064395582</v>
+        <v>3.249719034095576</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.914629007459533</v>
+        <v>4.542546627549992</v>
       </c>
       <c r="C2" t="n">
-        <v>9.235300653849745</v>
+        <v>8.612872609357268</v>
       </c>
       <c r="D2" t="n">
-        <v>21.82817845622358</v>
+        <v>23.08677901306799</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.38046044535803</v>
+        <v>14.63785827031994</v>
       </c>
       <c r="C3" t="n">
-        <v>34.32189974046849</v>
+        <v>23.77792939685775</v>
       </c>
       <c r="D3" t="n">
-        <v>44.68915549731481</v>
+        <v>46.3728528100981</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.51343835378785</v>
+        <v>21.36479353981909</v>
       </c>
       <c r="C4" t="n">
-        <v>56.50056212710818</v>
+        <v>51.28060958362789</v>
       </c>
       <c r="D4" t="n">
-        <v>35.68456555396306</v>
+        <v>36.89702396870788</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>10.25926350937917</v>
+        <v>10.01382658331747</v>
       </c>
       <c r="C5" t="n">
-        <v>43.81049130201392</v>
+        <v>36.98734475749859</v>
       </c>
       <c r="D5" t="n">
-        <v>31.58773238414113</v>
+        <v>31.71045084717198</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.916993413495527</v>
+        <v>5.957245069369646</v>
       </c>
       <c r="C6" t="n">
-        <v>12.3572583533546</v>
+        <v>12.27675504160637</v>
       </c>
       <c r="D6" t="n">
-        <v>36.10573531908495</v>
+        <v>36.54850353370026</v>
       </c>
     </row>
     <row r="7">
@@ -5204,7 +5204,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>9.521970983489814</v>
       </c>
       <c r="C7" t="n">
         <v>24.25407703341745</v>
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.34762080276138</v>
+        <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
-        <v>29.54078842078653</v>
+        <v>29.45733986592554</v>
       </c>
       <c r="D8" t="n">
-        <v>38.13598957146735</v>
+        <v>37.88564390688441</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>9.984374152190059</v>
       </c>
       <c r="C9" t="n">
-        <v>29.39843500367073</v>
+        <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>40.93593402397924</v>
+        <v>41.49062147687869</v>
       </c>
     </row>
     <row r="10">
@@ -5252,7 +5252,7 @@
         <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>48.9695754878309</v>
       </c>
     </row>
     <row r="11">
@@ -5266,7 +5266,7 @@
         <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>49.57727731675966</v>
       </c>
     </row>
     <row r="12">
@@ -5322,7 +5322,7 @@
         <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>43.00054944601029</v>
       </c>
     </row>
     <row r="16">
@@ -5336,7 +5336,7 @@
         <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>41.33157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.72178560587677</v>
+        <v>16.7248556518477</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0028921958483</v>
+        <v>102.021619476271</v>
       </c>
       <c r="D21" t="n">
-        <v>4.180446401469193</v>
+        <v>4.181213912961926</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.593998418798326</v>
+        <v>4.147884050442774</v>
       </c>
       <c r="C2" t="n">
-        <v>5.053055433758333</v>
+        <v>8.996735961717771</v>
       </c>
       <c r="D2" t="n">
-        <v>23.51776625523234</v>
+        <v>33.99792299806704</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.57680998620739</v>
+        <v>15.08946221427348</v>
       </c>
       <c r="C3" t="n">
-        <v>35.14165907351457</v>
+        <v>29.21681167838507</v>
       </c>
       <c r="D3" t="n">
-        <v>51.33558745506572</v>
+        <v>53.60342465187585</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.42708561354314</v>
+        <v>24.92559246312227</v>
       </c>
       <c r="C4" t="n">
-        <v>72.60711496298136</v>
+        <v>55.27534099220816</v>
       </c>
       <c r="D4" t="n">
-        <v>49.27686251926016</v>
+        <v>51.02535518052373</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>21.622993186036</v>
+        <v>21.00940087088174</v>
       </c>
       <c r="C5" t="n">
-        <v>75.44731107136739</v>
+        <v>68.15783436733483</v>
       </c>
       <c r="D5" t="n">
-        <v>36.71736413883072</v>
+        <v>37.20823799095412</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>9.821404033285093</v>
+        <v>9.700649065662736</v>
       </c>
       <c r="C6" t="n">
-        <v>41.90197376495812</v>
+        <v>36.26674194258143</v>
       </c>
       <c r="D6" t="n">
-        <v>38.31957639216151</v>
+        <v>38.68184129502858</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>21.31963314542373</v>
+        <v>21.02020009562846</v>
       </c>
       <c r="D7" t="n">
-        <v>39.76470901281281</v>
+        <v>39.52516257297658</v>
       </c>
     </row>
     <row r="8">
@@ -5532,10 +5532,10 @@
         <v>10.76486357706628</v>
       </c>
       <c r="C8" t="n">
-        <v>31.2097595180061</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D8" t="n">
-        <v>39.55461500410399</v>
+        <v>39.8884092235479</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>10.6499990956694</v>
       </c>
       <c r="C9" t="n">
-        <v>33.83593462686631</v>
+        <v>33.72499713628642</v>
       </c>
       <c r="D9" t="n">
-        <v>42.04530892977813</v>
+        <v>42.3781214015178</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.02599277086271</v>
+        <v>33.59540643932586</v>
       </c>
       <c r="D10" t="n">
-        <v>48.68486865359933</v>
+        <v>48.54251523648354</v>
       </c>
     </row>
     <row r="11">
@@ -5577,7 +5577,7 @@
         <v>33.93999988351647</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>50.6434553235717</v>
       </c>
     </row>
     <row r="12">
@@ -5585,10 +5585,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.159886007071988</v>
+        <v>7.376852249710534</v>
       </c>
       <c r="C12" t="n">
-        <v>34.28066633689012</v>
+        <v>33.84673385161303</v>
       </c>
       <c r="D12" t="n">
         <v>47.08167465256428</v>
@@ -5602,7 +5602,7 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>32.5203927031756</v>
+        <v>33.04071898642641</v>
       </c>
       <c r="D13" t="n">
         <v>45.78871292607123</v>
@@ -5630,10 +5630,10 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.38370878810703</v>
+        <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>43.00054944601029</v>
       </c>
     </row>
     <row r="16">
@@ -5644,10 +5644,10 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>41.74489413227862</v>
       </c>
     </row>
     <row r="17">
@@ -5686,10 +5686,10 @@
         <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
-        <v>25.27607639353838</v>
+        <v>24.67426505083508</v>
       </c>
     </row>
     <row r="20">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.0362693002688</v>
+        <v>18.04401628124632</v>
       </c>
       <c r="C21" t="n">
-        <v>117.6651854350869</v>
+        <v>117.7157252633689</v>
       </c>
       <c r="D21" t="n">
-        <v>6.012089766756267</v>
+        <v>6.014672093748773</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.862416452685205</v>
+        <v>5.508586368528853</v>
       </c>
       <c r="C2" t="n">
-        <v>7.39354196068273</v>
+        <v>6.547275439621979</v>
       </c>
       <c r="D2" t="n">
-        <v>20.22302095978005</v>
+        <v>32.75993914301181</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.94849145548944</v>
+        <v>12.92470852640926</v>
       </c>
       <c r="C3" t="n">
-        <v>24.74985962406209</v>
+        <v>30.42436135460865</v>
       </c>
       <c r="D3" t="n">
-        <v>54.36918786118836</v>
+        <v>63.51907646476863</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.58175978245763</v>
+        <v>19.62906359871073</v>
       </c>
       <c r="C4" t="n">
-        <v>67.70623042338129</v>
+        <v>54.38195058134357</v>
       </c>
       <c r="D4" t="n">
-        <v>55.05837474956962</v>
+        <v>57.20251173564466</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>19.21771131063132</v>
+        <v>17.79417713947344</v>
       </c>
       <c r="C5" t="n">
-        <v>78.39255418410782</v>
+        <v>63.37181430913162</v>
       </c>
       <c r="D5" t="n">
-        <v>36.93825737228624</v>
+        <v>37.45367491701582</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.465430527271</v>
+        <v>10.42517887139688</v>
       </c>
       <c r="C6" t="n">
-        <v>55.42653013866219</v>
+        <v>49.50953672516665</v>
       </c>
       <c r="D6" t="n">
-        <v>31.51704654943536</v>
+        <v>32.32207966691774</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.090361846519712</v>
+        <v>5.030475236560656</v>
       </c>
       <c r="C7" t="n">
-        <v>26.11056194214817</v>
+        <v>23.35577788403162</v>
       </c>
       <c r="D7" t="n">
-        <v>31.20092378866788</v>
+        <v>30.84160412891355</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.35868206941536</v>
+        <v>18.52557917913731</v>
       </c>
       <c r="D8" t="n">
-        <v>29.45733986592554</v>
+        <v>30.0414797499524</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>21.74374815365835</v>
+        <v>21.63281066307846</v>
       </c>
       <c r="D9" t="n">
-        <v>30.17499743772996</v>
+        <v>30.39687241888974</v>
       </c>
     </row>
     <row r="10">
@@ -5871,10 +5871,10 @@
         <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>21.06830573313655</v>
+        <v>21.35301256736813</v>
       </c>
       <c r="D10" t="n">
-        <v>33.16834618797849</v>
+        <v>33.02599277086271</v>
       </c>
     </row>
     <row r="11">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.820561154301086</v>
+        <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
-        <v>31.89403766786613</v>
+        <v>31.67707142522758</v>
       </c>
     </row>
     <row r="13">
@@ -5927,7 +5927,7 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
         <v>29.49955501720816</v>
@@ -5944,7 +5944,7 @@
         <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>27.95035713990669</v>
       </c>
     </row>
     <row r="16">
@@ -5958,7 +5958,7 @@
         <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -5969,7 +5969,7 @@
         <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
         <v>23.61103228713579</v>
@@ -5983,7 +5983,7 @@
         <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>17.12167996206437</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -5997,7 +5997,7 @@
         <v>1.203622685406589</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
         <v>15.64709491028566</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.044039002113897</v>
+        <v>7.048708421389251</v>
       </c>
       <c r="C21" t="n">
-        <v>66.03786564481778</v>
+        <v>66.08164145052423</v>
       </c>
       <c r="D21" t="n">
-        <v>4.402524376321185</v>
+        <v>4.405442763368281</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.924446484502001</v>
+        <v>4.437499623195583</v>
       </c>
       <c r="C2" t="n">
-        <v>6.181083545937918</v>
+        <v>5.546874528994478</v>
       </c>
       <c r="D2" t="n">
-        <v>20.72273054124167</v>
+        <v>40.11322944782042</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.79341637594744</v>
+        <v>16.73879835740812</v>
       </c>
       <c r="C3" t="n">
-        <v>27.36130851735861</v>
+        <v>27.3318560862312</v>
       </c>
       <c r="D3" t="n">
-        <v>58.21763886183585</v>
+        <v>75.68783925890784</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.55471281509523</v>
+        <v>23.24091340263474</v>
       </c>
       <c r="C4" t="n">
-        <v>64.29858414194059</v>
+        <v>67.96148482648545</v>
       </c>
       <c r="D4" t="n">
-        <v>70.78204598078653</v>
+        <v>77.21445693901164</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>26.89988709636261</v>
+        <v>24.44551783574558</v>
       </c>
       <c r="C5" t="n">
-        <v>106.5932569885975</v>
+        <v>85.78020565856507</v>
       </c>
       <c r="D5" t="n">
-        <v>48.69468613064181</v>
+        <v>49.87278337573798</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>19.07928488433252</v>
+        <v>18.31450342272425</v>
       </c>
       <c r="C6" t="n">
-        <v>95.47692773341082</v>
+        <v>78.69198723390311</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6290068454485</v>
+        <v>37.43403996293088</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.342311153612647</v>
+        <v>9.282424543653592</v>
       </c>
       <c r="C7" t="n">
-        <v>56.71261963122549</v>
+        <v>51.44259795482861</v>
       </c>
       <c r="D7" t="n">
-        <v>33.77604801690726</v>
+        <v>33.41672835715293</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.424156065963627</v>
+        <v>5.340707511102648</v>
       </c>
       <c r="C8" t="n">
-        <v>28.03871443328891</v>
+        <v>26.03594911662541</v>
       </c>
       <c r="D8" t="n">
-        <v>31.29320807286708</v>
+        <v>32.12769362147687</v>
       </c>
     </row>
     <row r="9">
@@ -6171,7 +6171,7 @@
         <v>23.07499804061703</v>
       </c>
       <c r="D9" t="n">
-        <v>31.39530983410874</v>
+        <v>31.72812230584841</v>
       </c>
     </row>
     <row r="10">
@@ -6182,7 +6182,7 @@
         <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>24.34243432679967</v>
+        <v>24.48478774391545</v>
       </c>
       <c r="D10" t="n">
         <v>33.31069960509428</v>
@@ -6193,10 +6193,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.909319358310797</v>
+        <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.10052348092744</v>
+        <v>23.27821981539612</v>
       </c>
       <c r="D11" t="n">
         <v>35.36157055926586</v>
@@ -6210,10 +6210,10 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>22.1305567491316</v>
+        <v>21.91359050649305</v>
       </c>
       <c r="D12" t="n">
-        <v>33.1958351236974</v>
+        <v>32.97886888105885</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>20.81305133003238</v>
+        <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>30.69925071179776</v>
       </c>
     </row>
     <row r="14">
@@ -6238,7 +6238,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>19.0517959486136</v>
+        <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
         <v>30.11412908006666</v>
@@ -6255,7 +6255,7 @@
         <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -6280,7 +6280,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
         <v>24.0832529328785</v>
@@ -6308,7 +6308,7 @@
         <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
         <v>15.64709491028566</v>
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.260392069357175</v>
+        <v>7.266334180773396</v>
       </c>
       <c r="C21" t="n">
-        <v>75.32656771958069</v>
+        <v>75.38821712552399</v>
       </c>
       <c r="D21" t="n">
-        <v>5.445294052017881</v>
+        <v>5.449750635580047</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.586324363613598</v>
+        <v>3.426299487821368</v>
       </c>
       <c r="C2" t="n">
-        <v>4.34914232981337</v>
+        <v>4.666246838285089</v>
       </c>
       <c r="D2" t="n">
-        <v>24.31494539108075</v>
+        <v>32.75699389989908</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.66302385773187</v>
+        <v>15.93376523992573</v>
       </c>
       <c r="C3" t="n">
-        <v>25.38308689330128</v>
+        <v>23.92519155249477</v>
       </c>
       <c r="D3" t="n">
-        <v>61.01561981893926</v>
+        <v>89.33904108645976</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.77841242294325</v>
+        <v>28.48639138642545</v>
       </c>
       <c r="C4" t="n">
-        <v>66.08536496366979</v>
+        <v>67.59136594198441</v>
       </c>
       <c r="D4" t="n">
-        <v>82.63861300497526</v>
+        <v>95.92460468654734</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.43480072645688</v>
+        <v>29.91876128692155</v>
       </c>
       <c r="C5" t="n">
-        <v>113.5391219961436</v>
+        <v>108.1395096227862</v>
       </c>
       <c r="D5" t="n">
-        <v>63.15092107567609</v>
+        <v>66.34160111447822</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.37741739125406</v>
+        <v>26.28433128579986</v>
       </c>
       <c r="C6" t="n">
-        <v>135.5273253281594</v>
+        <v>109.9272721922196</v>
       </c>
       <c r="D6" t="n">
-        <v>43.23027840880406</v>
+        <v>44.19631814978292</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.22927129890402</v>
+        <v>15.75017841923158</v>
       </c>
       <c r="C7" t="n">
-        <v>100.1304118515407</v>
+        <v>84.32034682235003</v>
       </c>
       <c r="D7" t="n">
-        <v>37.06981156465531</v>
+        <v>36.9500383447372</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.011061266653972</v>
+        <v>7.927612711792993</v>
       </c>
       <c r="C8" t="n">
-        <v>52.65603811727767</v>
+        <v>48.81740459367264</v>
       </c>
       <c r="D8" t="n">
-        <v>33.54631905411351</v>
+        <v>33.88011327355743</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>5.546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>29.84218496599028</v>
+        <v>28.51093507903161</v>
       </c>
       <c r="D9" t="n">
-        <v>32.28280975874785</v>
+        <v>33.17030968338697</v>
       </c>
     </row>
     <row r="10">
@@ -6493,7 +6493,7 @@
         <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
-        <v>26.62008900065227</v>
+        <v>26.76244241776806</v>
       </c>
       <c r="D10" t="n">
         <v>34.02246669067321</v>
@@ -6507,7 +6507,7 @@
         <v>4.264712027248144</v>
       </c>
       <c r="C11" t="n">
-        <v>25.9436648324262</v>
+        <v>26.12136116689488</v>
       </c>
       <c r="D11" t="n">
         <v>35.53926689373453</v>
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.06370009425158</v>
       </c>
     </row>
     <row r="13">
@@ -6538,7 +6538,7 @@
         <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
-        <v>31.47974013667398</v>
+        <v>31.21957699504857</v>
       </c>
     </row>
     <row r="14">
@@ -6563,10 +6563,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>18.99190933865455</v>
+        <v>19.35024725070463</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -6591,10 +6591,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -6619,10 +6619,10 @@
         <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.46315076855837</v>
+        <v>7.469732589303343</v>
       </c>
       <c r="C21" t="n">
-        <v>83.96044614628167</v>
+        <v>84.03449162966261</v>
       </c>
       <c r="D21" t="n">
-        <v>6.530256922488574</v>
+        <v>6.536016015640425</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_88_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_88_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.8449764891652</v>
+        <v>10.84497635042322</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907248879867</v>
+        <v>37.78907200535541</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.406664533736432</v>
+        <v>5.661739010391356</v>
       </c>
       <c r="C2" t="n">
-        <v>9.647634689633405</v>
+        <v>5.625414345334224</v>
       </c>
       <c r="D2" t="n">
-        <v>24.45631706049229</v>
+        <v>26.78796785807847</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.63156687346696</v>
+        <v>14.66731070144735</v>
       </c>
       <c r="C3" t="n">
-        <v>20.6854241284803</v>
+        <v>19.58095796120263</v>
       </c>
       <c r="D3" t="n">
-        <v>93.90907664972866</v>
+        <v>67.00428081484482</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.35425635697963</v>
+        <v>30.59224021203486</v>
       </c>
       <c r="C4" t="n">
-        <v>63.44348189154163</v>
+        <v>57.50881701936967</v>
       </c>
       <c r="D4" t="n">
-        <v>116.5619231775195</v>
+        <v>87.57778570504097</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.37375244234433</v>
+        <v>38.99992755120455</v>
       </c>
       <c r="C5" t="n">
-        <v>115.5271610972434</v>
+        <v>105.0960917396211</v>
       </c>
       <c r="D5" t="n">
-        <v>82.95768100885549</v>
+        <v>66.46431957750907</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.12711278440013</v>
+        <v>37.11202671593793</v>
       </c>
       <c r="C6" t="n">
-        <v>141.122305494662</v>
+        <v>139.4719876038232</v>
       </c>
       <c r="D6" t="n">
-        <v>54.13847715069036</v>
+        <v>46.93343074922303</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>23.29589127407256</v>
+        <v>26.58965482182061</v>
       </c>
       <c r="C7" t="n">
-        <v>120.6715190674967</v>
+        <v>130.732469540618</v>
       </c>
       <c r="D7" t="n">
-        <v>40.72289477215769</v>
+        <v>39.70482240285375</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.51728322914683</v>
+        <v>13.68556299720053</v>
       </c>
       <c r="C8" t="n">
-        <v>80.36095833112266</v>
+        <v>90.37478491444013</v>
       </c>
       <c r="D8" t="n">
-        <v>36.21667280966483</v>
+        <v>35.63253292563798</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.878124415953151</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>44.48593372253571</v>
+        <v>49.25624581747095</v>
       </c>
       <c r="D9" t="n">
-        <v>34.16874709860598</v>
+        <v>34.39062207976576</v>
       </c>
     </row>
     <row r="10">
@@ -895,10 +895,10 @@
         <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>30.60598467989432</v>
+        <v>32.02951885105219</v>
       </c>
       <c r="D10" t="n">
-        <v>34.87658719336794</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>28.96450251839364</v>
+        <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
-        <v>35.7169632282032</v>
+        <v>35.89465956267188</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.12078032981814</v>
+        <v>27.33774657245668</v>
       </c>
       <c r="D12" t="n">
-        <v>34.93156506480576</v>
+        <v>35.1485313074443</v>
       </c>
     </row>
     <row r="13">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>23.35381438862312</v>
+        <v>23.66110142005238</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -982,7 +982,7 @@
         <v>19.01252604044373</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -1007,10 +1007,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.658859791753085</v>
+        <v>7.673749404804173</v>
       </c>
       <c r="C21" t="n">
-        <v>92.86367497500616</v>
+        <v>93.04421153325059</v>
       </c>
       <c r="D21" t="n">
-        <v>7.658859791753085</v>
+        <v>7.673749404804173</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.310273332270997</v>
+        <v>6.801548095021903</v>
       </c>
       <c r="C2" t="n">
-        <v>8.035604959260143</v>
+        <v>8.927031874716247</v>
       </c>
       <c r="D2" t="n">
-        <v>26.12332466230338</v>
+        <v>27.81782119983337</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.55164439879547</v>
+        <v>16.65534980254714</v>
       </c>
       <c r="C3" t="n">
-        <v>29.03518835309941</v>
+        <v>20.64615422031042</v>
       </c>
       <c r="D3" t="n">
-        <v>91.45470738911162</v>
+        <v>71.60376880924112</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.32498385230147</v>
+        <v>28.95861203216817</v>
       </c>
       <c r="C4" t="n">
-        <v>57.5726306201457</v>
+        <v>53.14396672628834</v>
       </c>
       <c r="D4" t="n">
-        <v>133.8426462676719</v>
+        <v>99.05147112457344</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.58897617375263</v>
+        <v>42.01880174176349</v>
       </c>
       <c r="C5" t="n">
-        <v>114.9381124746953</v>
+        <v>104.4334120392545</v>
       </c>
       <c r="D5" t="n">
-        <v>101.3163630782709</v>
+        <v>79.44793296617314</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.21140421824511</v>
+        <v>44.63908636439822</v>
       </c>
       <c r="C6" t="n">
-        <v>161.0871268082252</v>
+        <v>152.916040665779</v>
       </c>
       <c r="D6" t="n">
-        <v>65.97246397768143</v>
+        <v>55.82904669740338</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>30.84160412891355</v>
+        <v>34.55457394637499</v>
       </c>
       <c r="C7" t="n">
-        <v>157.9209904620292</v>
+        <v>163.2508987483851</v>
       </c>
       <c r="D7" t="n">
-        <v>45.75337000871835</v>
+        <v>43.29801900039708</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>18.10833640483241</v>
+        <v>20.5283444958008</v>
       </c>
       <c r="C8" t="n">
-        <v>117.2452195796753</v>
+        <v>129.8459513636831</v>
       </c>
       <c r="D8" t="n">
-        <v>38.80357801035517</v>
+        <v>38.13598957146735</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>10.20624913334984</v>
       </c>
       <c r="C9" t="n">
-        <v>69.0031191406913</v>
+        <v>77.87811838708245</v>
       </c>
       <c r="D9" t="n">
-        <v>35.72187196672443</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.978843518863076</v>
+        <v>6.121196935978863</v>
       </c>
       <c r="C10" t="n">
-        <v>40.85543071223102</v>
+        <v>44.4142661401257</v>
       </c>
       <c r="D10" t="n">
-        <v>35.3036474447153</v>
+        <v>35.58835427894688</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>31.98534020436108</v>
+        <v>33.05151821117311</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>29.94134148411922</v>
+        <v>30.37527396939631</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>35.79943003535993</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
         <v>27.57729301229291</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>32.5203927031756</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>25.19753657719863</v>
+        <v>25.81211064005714</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.57528845915541</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.25247339090745</v>
+        <v>20.66578917439536</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -1304,7 +1304,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>18.41660518396592</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1321,7 +1321,7 @@
         <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.833297151273187</v>
+        <v>7.852985073188992</v>
       </c>
       <c r="C21" t="n">
-        <v>100.8537008226423</v>
+        <v>101.1071828173083</v>
       </c>
       <c r="D21" t="n">
-        <v>8.812459295182334</v>
+        <v>8.834608207337617</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.021058670145687</v>
+        <v>7.463246047684253</v>
       </c>
       <c r="C2" t="n">
-        <v>16.13502351929633</v>
+        <v>7.794095024015427</v>
       </c>
       <c r="D2" t="n">
-        <v>28.13688920371359</v>
+        <v>22.02550974477719</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.59367962362884</v>
+        <v>19.13426275577033</v>
       </c>
       <c r="C3" t="n">
-        <v>29.75186417719959</v>
+        <v>27.12568906833937</v>
       </c>
       <c r="D3" t="n">
-        <v>90.29624509810039</v>
+        <v>76.2278004962436</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.18084686622644</v>
+        <v>29.55845987946297</v>
       </c>
       <c r="C4" t="n">
-        <v>63.37966829076559</v>
+        <v>52.26333903557895</v>
       </c>
       <c r="D4" t="n">
-        <v>143.4529745445439</v>
+        <v>107.6280190688736</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.88350048502668</v>
+        <v>42.77965621255477</v>
       </c>
       <c r="C5" t="n">
-        <v>109.6857622569749</v>
+        <v>100.3100716814179</v>
       </c>
       <c r="D5" t="n">
-        <v>120.7058802371454</v>
+        <v>92.23519681398784</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>45.88688769649593</v>
+        <v>49.46928506929254</v>
       </c>
       <c r="C6" t="n">
-        <v>170.7072725621397</v>
+        <v>159.1147956703933</v>
       </c>
       <c r="D6" t="n">
-        <v>77.92720577229484</v>
+        <v>65.81145735418494</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>37.60879105428681</v>
+        <v>42.22006002113408</v>
       </c>
       <c r="C7" t="n">
-        <v>188.3433883212293</v>
+        <v>187.3852025618845</v>
       </c>
       <c r="D7" t="n">
-        <v>52.46067032413256</v>
+        <v>47.84940135728529</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>24.20008090968387</v>
+        <v>27.53802310412303</v>
       </c>
       <c r="C8" t="n">
-        <v>155.2977605962817</v>
+        <v>166.7302126122358</v>
       </c>
       <c r="D8" t="n">
-        <v>41.14013754646259</v>
+        <v>40.72289477215769</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>12.97968639784708</v>
+        <v>14.53281126596553</v>
       </c>
       <c r="C9" t="n">
-        <v>101.2859288994392</v>
+        <v>114.0437403161264</v>
       </c>
       <c r="D9" t="n">
-        <v>37.27499683484289</v>
+        <v>36.60937189136354</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.260024272905163</v>
+        <v>7.687084524252525</v>
       </c>
       <c r="C10" t="n">
-        <v>57.22607368054658</v>
+        <v>64.05903770210438</v>
       </c>
       <c r="D10" t="n">
-        <v>35.73070769606267</v>
+        <v>36.44247478164161</v>
       </c>
     </row>
     <row r="11">
@@ -1531,10 +1531,10 @@
         <v>5.153193699591506</v>
       </c>
       <c r="C11" t="n">
-        <v>38.02701557629594</v>
+        <v>40.51476425885736</v>
       </c>
       <c r="D11" t="n">
-        <v>36.78314123501524</v>
+        <v>36.25005223160922</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>32.76190263842031</v>
+        <v>33.62976760897449</v>
       </c>
       <c r="D12" t="n">
-        <v>35.36549755008285</v>
+        <v>36.23336252063703</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>29.65859814529614</v>
+        <v>29.91876128692155</v>
       </c>
       <c r="D13" t="n">
-        <v>33.30088212805181</v>
+        <v>32.780555844801</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>27.04125876577415</v>
+        <v>27.65583282863265</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>31.34327720578367</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>24.72531593145592</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.49242074137117</v>
+        <v>21.90573652485908</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -1615,7 +1615,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>19.36104647545135</v>
+        <v>19.83326712119407</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1629,10 +1629,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.992493163213184</v>
+        <v>8.017249497790278</v>
       </c>
       <c r="C21" t="n">
-        <v>108.8977193487796</v>
+        <v>109.2350244073925</v>
       </c>
       <c r="D21" t="n">
-        <v>9.990616454016481</v>
+        <v>10.02156187223785</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.468334712654734</v>
+        <v>6.792712365683681</v>
       </c>
       <c r="C2" t="n">
-        <v>11.10062129191869</v>
+        <v>5.299474107524283</v>
       </c>
       <c r="D2" t="n">
-        <v>23.37541283811655</v>
+        <v>18.20552942755285</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.45056544298705</v>
+        <v>21.91260875878881</v>
       </c>
       <c r="C3" t="n">
-        <v>47.88965301315941</v>
+        <v>38.81830422591889</v>
       </c>
       <c r="D3" t="n">
-        <v>99.29887154604364</v>
+        <v>82.96749848589795</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>19.15684295296801</v>
+        <v>20.54797944988574</v>
       </c>
       <c r="C4" t="n">
-        <v>88.81576956009619</v>
+        <v>79.16715312275853</v>
       </c>
       <c r="D4" t="n">
-        <v>137.0205635863188</v>
+        <v>103.4035586974995</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>25.84450831429729</v>
+        <v>27.85709110800325</v>
       </c>
       <c r="C5" t="n">
-        <v>102.0035864712436</v>
+        <v>95.05772146369743</v>
       </c>
       <c r="D5" t="n">
-        <v>79.00614649926207</v>
+        <v>64.10812508731674</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>23.34596040698915</v>
+        <v>26.20382797405162</v>
       </c>
       <c r="C6" t="n">
-        <v>124.0556034040355</v>
+        <v>123.4115769100496</v>
       </c>
       <c r="D6" t="n">
-        <v>34.5359207399943</v>
+        <v>31.51704654943536</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.9897248590678</v>
+        <v>18.20552942755285</v>
       </c>
       <c r="C7" t="n">
-        <v>109.1732899553581</v>
+        <v>117.2579822998305</v>
       </c>
       <c r="D7" t="n">
-        <v>28.92523261022377</v>
+        <v>28.62579956042849</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.012443924985718</v>
+        <v>10.09727513817844</v>
       </c>
       <c r="C8" t="n">
-        <v>74.60300804571511</v>
+        <v>84.03269474500573</v>
       </c>
       <c r="D8" t="n">
-        <v>27.45457454926205</v>
+        <v>26.95388322009618</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>5.435937038414587</v>
       </c>
       <c r="C9" t="n">
-        <v>43.59843379789659</v>
+        <v>48.92343334573128</v>
       </c>
       <c r="D9" t="n">
-        <v>27.17968519207294</v>
+        <v>27.73437264497238</v>
       </c>
     </row>
     <row r="10">
@@ -1828,10 +1828,10 @@
         <v>3.701188845010476</v>
       </c>
       <c r="C10" t="n">
-        <v>29.75186417719959</v>
+        <v>31.74481201682062</v>
       </c>
       <c r="D10" t="n">
-        <v>28.75539025738908</v>
+        <v>28.32833000604172</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>26.12136116689488</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
-        <v>28.25371718051895</v>
+        <v>28.96450251839364</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.169662426385451</v>
+        <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>24.0832529328785</v>
+        <v>24.30021917551705</v>
       </c>
       <c r="D12" t="n">
-        <v>27.12078032981814</v>
+        <v>26.68684784454105</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>22.37403017978481</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>20.28094407433061</v>
+        <v>20.58823110575986</v>
       </c>
       <c r="D14" t="n">
-        <v>24.58296251434014</v>
+        <v>23.66110142005238</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>18.27523351455437</v>
       </c>
       <c r="D15" t="n">
-        <v>22.21695054710532</v>
+        <v>22.93362637120549</v>
       </c>
     </row>
     <row r="16">
@@ -1912,7 +1912,7 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>16.94594712300419</v>
       </c>
       <c r="D16" t="n">
         <v>20.66578917439536</v>
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>15.58328130950962</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>17.47216389248049</v>
       </c>
     </row>
     <row r="18">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
       <c r="D19" t="n">
         <v>9.027170140549421</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.353650157707104</v>
+        <v>4.052654523130833</v>
       </c>
       <c r="C2" t="n">
-        <v>4.929355223023235</v>
+        <v>2.949170103557418</v>
       </c>
       <c r="D2" t="n">
-        <v>16.97245431101886</v>
+        <v>14.06353586333556</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.49121800948867</v>
+        <v>23.18888077430966</v>
       </c>
       <c r="C3" t="n">
-        <v>46.56429361242621</v>
+        <v>30.0267535343887</v>
       </c>
       <c r="D3" t="n">
-        <v>96.92304210176636</v>
+        <v>79.28103585645118</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.15532142591602</v>
+        <v>29.62227348023901</v>
       </c>
       <c r="C4" t="n">
-        <v>105.6242720045058</v>
+        <v>90.79399118415351</v>
       </c>
       <c r="D4" t="n">
-        <v>151.6083527237222</v>
+        <v>119.4845860930623</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.29887757491431</v>
+        <v>30.53235360207581</v>
       </c>
       <c r="C5" t="n">
-        <v>132.5113963807133</v>
+        <v>121.2458414744811</v>
       </c>
       <c r="D5" t="n">
-        <v>101.8808680082128</v>
+        <v>80.18424374435826</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>27.85414586489051</v>
+        <v>31.35603992593888</v>
       </c>
       <c r="C6" t="n">
-        <v>144.9462128027034</v>
+        <v>140.9210472152914</v>
       </c>
       <c r="D6" t="n">
-        <v>43.31078172055229</v>
+        <v>39.1246095096439</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.03153909972291</v>
+        <v>17.12757044828985</v>
       </c>
       <c r="C7" t="n">
-        <v>138.6973886651724</v>
+        <v>145.7041220303819</v>
       </c>
       <c r="D7" t="n">
-        <v>31.62013005838127</v>
+        <v>31.26081039862693</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.760715602071035</v>
+        <v>8.511752595819845</v>
       </c>
       <c r="C8" t="n">
-        <v>97.30101496790137</v>
+        <v>108.7334669838555</v>
       </c>
       <c r="D8" t="n">
-        <v>28.20561154301086</v>
+        <v>28.12216298814988</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.437499623195581</v>
+        <v>4.548437113775471</v>
       </c>
       <c r="C9" t="n">
-        <v>48.8124958551514</v>
+        <v>55.69062027110455</v>
       </c>
       <c r="D9" t="n">
-        <v>28.17812260729194</v>
+        <v>28.6218725696115</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>32.17187226816798</v>
+        <v>33.88011327355743</v>
       </c>
       <c r="D10" t="n">
-        <v>29.89421759431538</v>
+        <v>29.75186417719959</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>28.78680618392497</v>
+        <v>29.31989518733098</v>
       </c>
       <c r="D11" t="n">
-        <v>29.31989518733098</v>
+        <v>29.67528785626833</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>20.39482680802324</v>
+        <v>21.04572553593887</v>
       </c>
       <c r="D12" t="n">
-        <v>28.20561154301086</v>
+        <v>28.42257778564941</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.65044106402591</v>
+        <v>16.91060420565131</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>24.97566159603886</v>
       </c>
     </row>
     <row r="14">
@@ -2198,7 +2198,7 @@
         <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
-        <v>18.4372218857551</v>
+        <v>19.0517959486136</v>
       </c>
     </row>
     <row r="15">
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>14.33351648200343</v>
       </c>
       <c r="D15" t="n">
         <v>17.5585576904542</v>
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>13.22610507161303</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>13.9113649691773</v>
       </c>
       <c r="D18" t="n">
         <v>7.490734983403163</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.314380249537232</v>
+        <v>3.765984193490764</v>
       </c>
       <c r="C2" t="n">
-        <v>5.725552611167398</v>
+        <v>12.13440162449058</v>
       </c>
       <c r="D2" t="n">
-        <v>17.51732428687584</v>
+        <v>16.82322865997334</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.92747384307275</v>
+        <v>18.42740440871263</v>
       </c>
       <c r="C3" t="n">
-        <v>32.40258297866598</v>
+        <v>19.96874830438012</v>
       </c>
       <c r="D3" t="n">
-        <v>88.76471867947537</v>
+        <v>73.29237486054562</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.08173140582652</v>
+        <v>36.96083756948391</v>
       </c>
       <c r="C4" t="n">
-        <v>110.8314618278309</v>
+        <v>83.41713893444297</v>
       </c>
       <c r="D4" t="n">
-        <v>163.3755807068245</v>
+        <v>129.9883047807989</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.64311116620645</v>
+        <v>36.96280106489242</v>
       </c>
       <c r="C5" t="n">
-        <v>162.2828955119978</v>
+        <v>143.8014949795516</v>
       </c>
       <c r="D5" t="n">
-        <v>127.8971821707532</v>
+        <v>99.94191629232532</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>32.48308629041422</v>
+        <v>36.06548366321083</v>
       </c>
       <c r="C6" t="n">
-        <v>176.906027566754</v>
+        <v>165.6355639220006</v>
       </c>
       <c r="D6" t="n">
-        <v>60.53849043467533</v>
+        <v>52.76992085097032</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.21793229480956</v>
+        <v>25.45180923259856</v>
       </c>
       <c r="C7" t="n">
-        <v>172.4135500721206</v>
+        <v>175.2282207401962</v>
       </c>
       <c r="D7" t="n">
-        <v>35.75230614555609</v>
+        <v>35.15344004596554</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>12.2669375645639</v>
       </c>
       <c r="C8" t="n">
-        <v>135.7707987588126</v>
+        <v>148.5384276525424</v>
       </c>
       <c r="D8" t="n">
-        <v>29.87458264023044</v>
+        <v>29.79113408536946</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.546874528994477</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>78.4328058399819</v>
+        <v>90.63592980376974</v>
       </c>
       <c r="D9" t="n">
-        <v>29.17656002251095</v>
+        <v>29.28749751309084</v>
       </c>
     </row>
     <row r="10">
@@ -2450,10 +2450,10 @@
         <v>2.704714925199962</v>
       </c>
       <c r="C10" t="n">
-        <v>42.84837855185204</v>
+        <v>46.97662764820988</v>
       </c>
       <c r="D10" t="n">
-        <v>30.17892442854695</v>
+        <v>30.46363126277853</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>32.51842920776709</v>
+        <v>34.11769621798515</v>
       </c>
       <c r="D11" t="n">
-        <v>29.852984190737</v>
+        <v>30.20837685967435</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>25.16808414607123</v>
       </c>
       <c r="D12" t="n">
-        <v>28.63954402828795</v>
+        <v>28.8565102709265</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.73174619702914</v>
+        <v>19.25207248027995</v>
       </c>
       <c r="D13" t="n">
-        <v>26.53664044579129</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.28621266575034</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>19.35908298004286</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.40853021815369</v>
+        <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -2537,7 +2537,7 @@
         <v>14.46605242207675</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -2551,7 +2551,7 @@
         <v>14.63884001802419</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>11.33329549782518</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>34.24335992412875</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>34.3032465340878</v>
+        <v>34.9050578767911</v>
       </c>
       <c r="D19" t="n">
         <v>3.610868056219768</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.971349390127595</v>
+        <v>2.235439522569987</v>
       </c>
       <c r="C2" t="n">
-        <v>2.727295122397639</v>
+        <v>5.557673753741193</v>
       </c>
       <c r="D2" t="n">
-        <v>12.2335581426195</v>
+        <v>11.62389281828223</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.7753029489145</v>
+        <v>17.86780821729195</v>
       </c>
       <c r="C3" t="n">
-        <v>30.2280118137593</v>
+        <v>33.33033455917921</v>
       </c>
       <c r="D3" t="n">
-        <v>86.64905237682348</v>
+        <v>72.74259614616741</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.22136056400782</v>
+        <v>40.75136545558085</v>
       </c>
       <c r="C4" t="n">
-        <v>110.7421227867444</v>
+        <v>79.90739089176064</v>
       </c>
       <c r="D4" t="n">
-        <v>172.7051291402819</v>
+        <v>139.8283620204647</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.23845118560752</v>
+        <v>38.68085954732433</v>
       </c>
       <c r="C5" t="n">
-        <v>198.8529974951915</v>
+        <v>168.5906245117835</v>
       </c>
       <c r="D5" t="n">
-        <v>134.5730665596316</v>
+        <v>105.6360529769568</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>26.68684784454105</v>
+        <v>30.43025184083414</v>
       </c>
       <c r="C6" t="n">
-        <v>210.6369151892659</v>
+        <v>204.7199217757704</v>
       </c>
       <c r="D6" t="n">
-        <v>58.68691426446584</v>
+        <v>51.80388110999145</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.186393195086651</v>
+        <v>8.084692344472483</v>
       </c>
       <c r="C7" t="n">
-        <v>180.0191495369206</v>
+        <v>187.8044088315978</v>
       </c>
       <c r="D7" t="n">
-        <v>35.51275970571987</v>
+        <v>35.03366682604743</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.838633523605028</v>
+        <v>4.005530633326986</v>
       </c>
       <c r="C8" t="n">
-        <v>97.71825774220626</v>
+        <v>113.3231375012093</v>
       </c>
       <c r="D8" t="n">
-        <v>31.37665662772806</v>
+        <v>31.46010518258904</v>
       </c>
     </row>
     <row r="9">
@@ -2747,10 +2747,10 @@
         <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>32.61562223048752</v>
+        <v>35.83280945730432</v>
       </c>
       <c r="D9" t="n">
-        <v>31.61718481526852</v>
+        <v>31.8390597964283</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>25.48126166372597</v>
+        <v>26.76244241776806</v>
       </c>
       <c r="D10" t="n">
-        <v>23.34596040698915</v>
+        <v>23.63066724122073</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>19.72429312602266</v>
+        <v>20.07968579496001</v>
       </c>
       <c r="D11" t="n">
-        <v>22.92282714645877</v>
+        <v>23.10052348092744</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.18763698469816</v>
+        <v>15.62156946997525</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>21.04572553593887</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>13.52848336452105</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>12.90605532002857</v>
+        <v>13.21334235145782</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -2834,7 +2834,7 @@
         <v>12.18348900970292</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>12.18348900970292</v>
       </c>
     </row>
     <row r="16">
@@ -2848,7 +2848,7 @@
         <v>12.39947350463721</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>9.506263020221864</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29.42788743479814</v>
+        <v>29.96293993361265</v>
       </c>
       <c r="D18" t="n">
         <v>2.675262494072558</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.701769682087222</v>
+        <v>3.675663404700058</v>
       </c>
       <c r="C2" t="n">
-        <v>6.516841260790327</v>
+        <v>7.36212603414683</v>
       </c>
       <c r="D2" t="n">
-        <v>17.06081160440107</v>
+        <v>18.56386733960294</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.9563043793944</v>
+        <v>12.88543861823939</v>
       </c>
       <c r="C3" t="n">
-        <v>20.43507846389736</v>
+        <v>27.3318560862312</v>
       </c>
       <c r="D3" t="n">
-        <v>78.19129590473722</v>
+        <v>65.86545347791851</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.83473189498382</v>
+        <v>38.04566878267665</v>
       </c>
       <c r="C4" t="n">
-        <v>93.6145523384546</v>
+        <v>82.2429686801638</v>
       </c>
       <c r="D4" t="n">
-        <v>175.525690294583</v>
+        <v>143.6188899065617</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.86524818927349</v>
+        <v>48.32653074154926</v>
       </c>
       <c r="C5" t="n">
-        <v>202.8536193899972</v>
+        <v>159.9512447144116</v>
       </c>
       <c r="D5" t="n">
-        <v>158.9204096249524</v>
+        <v>128.5107744859075</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.29441080474959</v>
+        <v>39.24536447726626</v>
       </c>
       <c r="C6" t="n">
-        <v>258.4558823677196</v>
+        <v>235.1501736166045</v>
       </c>
       <c r="D6" t="n">
-        <v>80.26180181299375</v>
+        <v>67.42152358914971</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>14.73210604992764</v>
+        <v>17.0676838383308</v>
       </c>
       <c r="C7" t="n">
-        <v>235.7136967988422</v>
+        <v>236.4323361183508</v>
       </c>
       <c r="D7" t="n">
-        <v>41.20198765183014</v>
+        <v>40.36357511240336</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.923464736797754</v>
+        <v>5.424156065963627</v>
       </c>
       <c r="C8" t="n">
-        <v>153.5453409442011</v>
+        <v>171.8205744587555</v>
       </c>
       <c r="D8" t="n">
-        <v>33.29597338953057</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.218749811597791</v>
+        <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>64.01093206459626</v>
+        <v>73.99530621678632</v>
       </c>
       <c r="D9" t="n">
-        <v>32.39374724932775</v>
+        <v>33.05937219280708</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>30.7483380970101</v>
+        <v>32.74128593663113</v>
       </c>
       <c r="D10" t="n">
-        <v>24.62714116103124</v>
+        <v>24.76949457814703</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>22.92282714645877</v>
+        <v>23.98900515327081</v>
       </c>
       <c r="D11" t="n">
-        <v>23.63361248433346</v>
+        <v>23.81130881880213</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.57426565372215</v>
+        <v>17.7912318963607</v>
       </c>
       <c r="D12" t="n">
-        <v>21.69662426385451</v>
+        <v>21.47965802121596</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>15.08946221427348</v>
+        <v>15.86995163914969</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.52062938288707</v>
+        <v>13.82791641431633</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>14.13520344574558</v>
       </c>
     </row>
     <row r="15">
@@ -3156,7 +3156,7 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.97231544229862</v>
+        <v>23.55899965881071</v>
       </c>
       <c r="D16" t="n">
         <v>8.266315669758143</v>
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="D18" t="n">
         <v>1.070104997629023</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.721003725544659</v>
+        <v>2.418044595559894</v>
       </c>
       <c r="C2" t="n">
-        <v>3.372303364087794</v>
+        <v>3.984913931537803</v>
       </c>
       <c r="D2" t="n">
-        <v>12.48292205949819</v>
+        <v>13.10338660858218</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.29853341754904</v>
+        <v>12.86580366415445</v>
       </c>
       <c r="C3" t="n">
-        <v>23.04161861867264</v>
+        <v>28.20561154301086</v>
       </c>
       <c r="D3" t="n">
-        <v>75.54057710327082</v>
+        <v>65.51202430438966</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.52918737478481</v>
+        <v>33.7956829709922</v>
       </c>
       <c r="C4" t="n">
-        <v>78.42691535375644</v>
+        <v>78.27376271189394</v>
       </c>
       <c r="D4" t="n">
-        <v>175.3342494922549</v>
+        <v>144.3336022352533</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.32590884674349</v>
+        <v>53.16163818496479</v>
       </c>
       <c r="C5" t="n">
-        <v>196.5704340828177</v>
+        <v>162.1110896637546</v>
       </c>
       <c r="D5" t="n">
-        <v>176.0028196788469</v>
+        <v>144.0714755982195</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.92964262712628</v>
+        <v>46.249152599363</v>
       </c>
       <c r="C6" t="n">
-        <v>291.5024918403715</v>
+        <v>253.3841737275806</v>
       </c>
       <c r="D6" t="n">
-        <v>94.71214627180255</v>
+        <v>80.30205346886787</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>13.29482741091031</v>
+        <v>15.92983824910874</v>
       </c>
       <c r="C7" t="n">
-        <v>286.7370884839574</v>
+        <v>280.3292212183385</v>
       </c>
       <c r="D7" t="n">
-        <v>46.47200932822701</v>
+        <v>45.75337000871835</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.005530633326986</v>
+        <v>4.506221962492859</v>
       </c>
       <c r="C8" t="n">
-        <v>195.5199640392735</v>
+        <v>213.7951975538279</v>
       </c>
       <c r="D8" t="n">
-        <v>34.54770171244525</v>
+        <v>34.04701038327938</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.664062358698343</v>
+        <v>1.774999849278233</v>
       </c>
       <c r="C9" t="n">
-        <v>72.33124385808797</v>
+        <v>85.97655519941439</v>
       </c>
       <c r="D9" t="n">
-        <v>31.94999728700819</v>
+        <v>32.8374972116473</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>31.17539834835747</v>
+        <v>33.59540643932586</v>
       </c>
       <c r="D10" t="n">
-        <v>25.33890824661018</v>
+        <v>25.19655482949439</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.7451308119901</v>
+        <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -3411,7 +3411,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.70640068316797</v>
+        <v>17.57426565372215</v>
       </c>
       <c r="D12" t="n">
         <v>19.96089432274615</v>
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.18701508989241</v>
+        <v>11.44717823151781</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>16.1301147807751</v>
       </c>
     </row>
     <row r="14">
@@ -3453,7 +3453,7 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
         <v>6.808420328951629</v>
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
         <v>0.4722206457427158</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.14217349066654</v>
+        <v>3.219150722225291</v>
       </c>
       <c r="C2" t="n">
-        <v>15.17683775995144</v>
+        <v>5.749114556069322</v>
       </c>
       <c r="D2" t="n">
-        <v>22.36813969355933</v>
+        <v>18.89275282052562</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>8.177958376375932</v>
+        <v>10.59305772882308</v>
       </c>
       <c r="C3" t="n">
-        <v>18.40776945462769</v>
+        <v>22.06477965294707</v>
       </c>
       <c r="D3" t="n">
-        <v>69.85134915716056</v>
+        <v>61.31505286873454</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.68760860806704</v>
+        <v>29.25215459573796</v>
       </c>
       <c r="C4" t="n">
-        <v>69.14841780091984</v>
+        <v>74.50876026610743</v>
       </c>
       <c r="D4" t="n">
-        <v>171.1480772813465</v>
+        <v>143.6827035073377</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.54051068334605</v>
+        <v>52.71985171805373</v>
       </c>
       <c r="C5" t="n">
-        <v>174.4565670446582</v>
+        <v>153.9380400258999</v>
       </c>
       <c r="D5" t="n">
-        <v>192.299831569344</v>
+        <v>156.2451471308799</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>47.05418571684538</v>
+        <v>55.30577517103983</v>
       </c>
       <c r="C6" t="n">
-        <v>300.6396177237966</v>
+        <v>256.0810346711465</v>
       </c>
       <c r="D6" t="n">
-        <v>117.6958417759246</v>
+        <v>100.1863714706828</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.13430381349934</v>
+        <v>29.46421209985527</v>
       </c>
       <c r="C7" t="n">
-        <v>339.8565115176395</v>
+        <v>319.854383791315</v>
       </c>
       <c r="D7" t="n">
-        <v>57.07193929097983</v>
+        <v>54.67647489261761</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.009678608322226</v>
+        <v>8.344855486097888</v>
       </c>
       <c r="C8" t="n">
-        <v>267.2857212197154</v>
+        <v>276.0478194801181</v>
       </c>
       <c r="D8" t="n">
-        <v>37.38495257771854</v>
+        <v>37.1346069131356</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.218749811597791</v>
+        <v>2.551562283337459</v>
       </c>
       <c r="C9" t="n">
-        <v>131.7937388089088</v>
+        <v>152.7609245285079</v>
       </c>
       <c r="D9" t="n">
-        <v>32.9484347022272</v>
+        <v>34.05780960802609</v>
       </c>
     </row>
     <row r="10">
@@ -3691,10 +3691,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.7117670855789376</v>
       </c>
       <c r="C10" t="n">
-        <v>48.9695754878309</v>
+        <v>57.08372026343079</v>
       </c>
       <c r="D10" t="n">
         <v>26.33538216642069</v>
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>27.00984283923824</v>
+        <v>28.96450251839364</v>
       </c>
       <c r="D11" t="n">
-        <v>24.34439782220815</v>
+        <v>24.52209415667683</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.30999559483051</v>
+        <v>20.39482680802324</v>
       </c>
       <c r="D12" t="n">
-        <v>20.39482680802324</v>
+        <v>20.17786056538469</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.00815708127024</v>
+        <v>13.52848336452105</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -3753,7 +3753,7 @@
         <v>11.67690719431156</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>11.36962016288231</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>20.42526098685489</v>
       </c>
       <c r="D15" t="n">
         <v>6.450082416901544</v>
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>27.27884171020187</v>
+        <v>28.10547327717769</v>
       </c>
       <c r="D16" t="n">
         <v>2.89321048441535</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.41982816451914</v>
+        <v>4.706498494159209</v>
       </c>
       <c r="C2" t="n">
-        <v>8.420450059324892</v>
+        <v>10.97692108118359</v>
       </c>
       <c r="D2" t="n">
-        <v>19.43173231015712</v>
+        <v>10.82573193472958</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.54821612959722</v>
+        <v>2.30219836645877</v>
       </c>
       <c r="C2" t="n">
-        <v>8.86420002164445</v>
+        <v>3.265292864324891</v>
       </c>
       <c r="D2" t="n">
-        <v>16.64258708239193</v>
+        <v>13.90547448295182</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.84831213192725</v>
+        <v>13.98499604699582</v>
       </c>
       <c r="C3" t="n">
-        <v>32.47130531796326</v>
+        <v>25.52053157189584</v>
       </c>
       <c r="D3" t="n">
-        <v>77.73969196078369</v>
+        <v>68.6192557883308</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.80019079888594</v>
+        <v>40.26638208968293</v>
       </c>
       <c r="C4" t="n">
-        <v>100.123539617611</v>
+        <v>102.1655748424443</v>
       </c>
       <c r="D4" t="n">
-        <v>176.7891995899486</v>
+        <v>147.7667739570044</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.29258617806133</v>
+        <v>32.61856747360028</v>
       </c>
       <c r="C5" t="n">
-        <v>256.0398012675682</v>
+        <v>222.9058162492383</v>
       </c>
       <c r="D5" t="n">
-        <v>174.3093048890212</v>
+        <v>142.427048193606</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>14.97361598517235</v>
+        <v>18.27425176685013</v>
       </c>
       <c r="C6" t="n">
-        <v>279.8295116368769</v>
+        <v>260.8709817201668</v>
       </c>
       <c r="D6" t="n">
-        <v>89.19766941704822</v>
+        <v>80.42280843649023</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4.611268966847268</v>
+        <v>5.509568116233099</v>
       </c>
       <c r="C7" t="n">
-        <v>187.9241820515159</v>
+        <v>194.0925028772986</v>
       </c>
       <c r="D7" t="n">
-        <v>33.53650157707104</v>
+        <v>33.0574086973986</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.50207398749762</v>
+        <v>1.752419652080557</v>
       </c>
       <c r="C8" t="n">
-        <v>97.13411785817941</v>
+        <v>112.5721005074605</v>
       </c>
       <c r="D8" t="n">
-        <v>24.28352946454485</v>
+        <v>25.03456645829366</v>
       </c>
     </row>
     <row r="9">
@@ -4299,10 +4299,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3328124717396686</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>37.38593432542277</v>
+        <v>43.4874963073167</v>
       </c>
       <c r="D9" t="n">
         <v>20.07968579496001</v>
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>21.06830573313655</v>
+        <v>22.63419332141022</v>
       </c>
       <c r="D10" t="n">
-        <v>19.07535789351553</v>
+        <v>19.21771131063132</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.45958109877452</v>
+        <v>16.34806277111788</v>
       </c>
       <c r="D11" t="n">
-        <v>16.34806277111788</v>
+        <v>16.17036643664921</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.63134588928871</v>
+        <v>10.84831213192725</v>
       </c>
       <c r="D12" t="n">
-        <v>13.4519070435898</v>
+        <v>13.23494080095125</v>
       </c>
     </row>
     <row r="13">
@@ -4361,7 +4361,7 @@
         <v>9.626036240139976</v>
       </c>
       <c r="D13" t="n">
-        <v>9.105709956889166</v>
+        <v>9.365873098514571</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
         <v>5.223879534297279</v>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>22.93362637120549</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
         <v>2.150027472300515</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.481097432809942</v>
+        <v>6.708282063118455</v>
       </c>
       <c r="C2" t="n">
-        <v>7.420049148697394</v>
+        <v>4.978442608235575</v>
       </c>
       <c r="D2" t="n">
-        <v>23.58157985600839</v>
+        <v>20.16313434982099</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.395325529641976</v>
+        <v>10.004009106275</v>
       </c>
       <c r="C3" t="n">
-        <v>21.21556788877357</v>
+        <v>27.66074156715388</v>
       </c>
       <c r="D3" t="n">
-        <v>19.45823949817178</v>
+        <v>12.22766765639402</v>
       </c>
     </row>
     <row r="4">
@@ -4557,7 +4557,7 @@
         <v>4.736932672990861</v>
       </c>
       <c r="C5" t="n">
-        <v>9.449321653375552</v>
+        <v>9.35114688295087</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4571,7 +4571,7 @@
         <v>8.050331174823848</v>
       </c>
       <c r="C6" t="n">
-        <v>18.27425176685013</v>
+        <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
         <v>32.8453511932813</v>
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.845546815263761</v>
+        <v>8.762098260402782</v>
       </c>
       <c r="C8" t="n">
         <v>21.69662426385451</v>
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.764061755811273</v>
+        <v>8.874999246391162</v>
       </c>
       <c r="C9" t="n">
         <v>22.74218556887735</v>
       </c>
       <c r="D9" t="n">
-        <v>39.60468413702056</v>
+        <v>39.2718716652809</v>
       </c>
     </row>
     <row r="10">
@@ -4630,7 +4630,7 @@
         <v>25.62361508084176</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>50.67781649322036</v>
       </c>
     </row>
     <row r="11">
@@ -4697,7 +4697,7 @@
         <v>5.375068680751286</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>26.15866757965626</v>
       </c>
       <c r="D15" t="n">
         <v>42.28387362191012</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39646475635912</v>
+        <v>13.3974514252656</v>
       </c>
       <c r="C21" t="n">
-        <v>70.13443313623307</v>
+        <v>70.13959863815519</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576054677218721</v>
+        <v>1.5761707559136</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.122358610132356</v>
+        <v>4.233296100712247</v>
       </c>
       <c r="C2" t="n">
-        <v>5.723589115758905</v>
+        <v>7.323837873681205</v>
       </c>
       <c r="D2" t="n">
-        <v>24.79207477534471</v>
+        <v>16.34119053718816</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.09927969131594</v>
+        <v>17.85799074024948</v>
       </c>
       <c r="C3" t="n">
-        <v>26.04576659366788</v>
+        <v>22.50165738133689</v>
       </c>
       <c r="D3" t="n">
-        <v>34.56242792800896</v>
+        <v>26.20775496486861</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>11.03975293425538</v>
+        <v>11.72893982263664</v>
       </c>
       <c r="C4" t="n">
-        <v>32.8895298399724</v>
+        <v>42.69129891917255</v>
       </c>
       <c r="D4" t="n">
-        <v>25.2701859073129</v>
+        <v>21.47965802121596</v>
       </c>
     </row>
     <row r="5">
@@ -4868,7 +4868,7 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.522330836388309</v>
+        <v>5.473243451175969</v>
       </c>
       <c r="D5" t="n">
         <v>29.40334374219198</v>
@@ -4893,10 +4893,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>24.3139636433765</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
         <v>34.97378021608837</v>
@@ -4907,7 +4907,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.513135254151592</v>
+        <v>9.596583809012571</v>
       </c>
       <c r="C8" t="n">
         <v>25.61870634232051</v>
@@ -4927,7 +4927,7 @@
         <v>25.73749781453438</v>
       </c>
       <c r="D9" t="n">
-        <v>40.60312155223957</v>
+        <v>40.27030908049991</v>
       </c>
     </row>
     <row r="10">
@@ -4941,7 +4941,7 @@
         <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
-        <v>49.68134257340984</v>
+        <v>50.1084028247572</v>
       </c>
     </row>
     <row r="11">
@@ -4952,7 +4952,7 @@
         <v>7.640942382152923</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>29.14219885286231</v>
       </c>
       <c r="D11" t="n">
         <v>47.97801030654161</v>
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>28.8565102709265</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -5022,7 +5022,7 @@
         <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
         <v>40.91826256530281</v>
@@ -5036,7 +5036,7 @@
         <v>5.66664774891259</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>31.63878326476196</v>
       </c>
       <c r="D17" t="n">
         <v>36.36098972218912</v>
@@ -5050,7 +5050,7 @@
         <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>31.56809743005619</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43616541195399</v>
+        <v>15.43806771707706</v>
       </c>
       <c r="C21" t="n">
-        <v>86.11755440353278</v>
+        <v>86.12816726369309</v>
       </c>
       <c r="D21" t="n">
-        <v>3.249719034095576</v>
+        <v>3.250119519384645</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.542546627549992</v>
+        <v>4.66919208139783</v>
       </c>
       <c r="C2" t="n">
-        <v>8.612872609357268</v>
+        <v>7.637997139040184</v>
       </c>
       <c r="D2" t="n">
-        <v>23.08677901306799</v>
+        <v>17.88646142367264</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.63785827031994</v>
+        <v>16.05648370295658</v>
       </c>
       <c r="C3" t="n">
-        <v>23.77792939685775</v>
+        <v>26.13903262557133</v>
       </c>
       <c r="D3" t="n">
-        <v>46.3728528100981</v>
+        <v>33.19779861910589</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.36479353981909</v>
+        <v>24.6703380600181</v>
       </c>
       <c r="C4" t="n">
-        <v>51.28060958362789</v>
+        <v>50.75733805726435</v>
       </c>
       <c r="D4" t="n">
-        <v>36.89702396870788</v>
+        <v>29.77542612210151</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>10.01382658331747</v>
+        <v>10.55378782065321</v>
       </c>
       <c r="C5" t="n">
-        <v>36.98734475749859</v>
+        <v>47.27115195948392</v>
       </c>
       <c r="D5" t="n">
-        <v>31.71045084717198</v>
+        <v>30.38509144643879</v>
       </c>
     </row>
     <row r="6">
@@ -5193,7 +5193,7 @@
         <v>5.957245069369646</v>
       </c>
       <c r="C6" t="n">
-        <v>12.27675504160637</v>
+        <v>12.23650338573225</v>
       </c>
       <c r="D6" t="n">
         <v>36.54850353370026</v>
@@ -5204,10 +5204,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>24.25407703341745</v>
+        <v>24.13430381349934</v>
       </c>
       <c r="D7" t="n">
         <v>37.4890178343687</v>
@@ -5221,7 +5221,7 @@
         <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
-        <v>29.45733986592554</v>
+        <v>29.87458264023044</v>
       </c>
       <c r="D8" t="n">
         <v>37.88564390688441</v>
@@ -5238,7 +5238,7 @@
         <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>41.49062147687869</v>
+        <v>41.15780900513902</v>
       </c>
     </row>
     <row r="10">
@@ -5252,7 +5252,7 @@
         <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
-        <v>48.9695754878309</v>
+        <v>49.25428232206248</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>8.174031385558941</v>
       </c>
       <c r="C11" t="n">
-        <v>31.45225120095506</v>
+        <v>30.91916219754903</v>
       </c>
       <c r="D11" t="n">
-        <v>49.57727731675966</v>
+        <v>49.75497365122833</v>
       </c>
     </row>
     <row r="12">
@@ -5277,7 +5277,7 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>31.46010518258904</v>
+        <v>31.89403766786613</v>
       </c>
       <c r="D12" t="n">
         <v>46.2138096820101</v>
@@ -5291,7 +5291,7 @@
         <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
         <v>45.00822350119503</v>
@@ -5319,7 +5319,7 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
         <v>43.00054944601029</v>
@@ -5333,7 +5333,7 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
         <v>41.33157834879071</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.7248556518477</v>
+        <v>16.72855287651986</v>
       </c>
       <c r="C21" t="n">
-        <v>102.021619476271</v>
+        <v>102.0441725467712</v>
       </c>
       <c r="D21" t="n">
-        <v>4.181213912961926</v>
+        <v>4.182138219129966</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.147884050442774</v>
+        <v>4.50327671938012</v>
       </c>
       <c r="C2" t="n">
-        <v>8.996735961717771</v>
+        <v>6.893832379221102</v>
       </c>
       <c r="D2" t="n">
-        <v>33.99792299806704</v>
+        <v>27.36523550817559</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.08946221427348</v>
+        <v>15.97794388661684</v>
       </c>
       <c r="C3" t="n">
-        <v>29.21681167838507</v>
+        <v>28.14670668075605</v>
       </c>
       <c r="D3" t="n">
-        <v>53.60342465187585</v>
+        <v>39.40735284846697</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.92559246312227</v>
+        <v>27.91206897944107</v>
       </c>
       <c r="C4" t="n">
-        <v>55.27534099220816</v>
+        <v>58.93824167675302</v>
       </c>
       <c r="D4" t="n">
-        <v>51.02535518052373</v>
+        <v>39.1815508764902</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>21.00940087088174</v>
+        <v>23.73375075016664</v>
       </c>
       <c r="C5" t="n">
-        <v>68.15783436733483</v>
+        <v>72.3793494955961</v>
       </c>
       <c r="D5" t="n">
-        <v>37.20823799095412</v>
+        <v>33.79666471869646</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>9.700649065662736</v>
+        <v>10.06291396852981</v>
       </c>
       <c r="C6" t="n">
-        <v>36.26674194258143</v>
+        <v>44.55858305264999</v>
       </c>
       <c r="D6" t="n">
-        <v>38.68184129502858</v>
+        <v>38.31957639216151</v>
       </c>
     </row>
     <row r="7">
@@ -5515,10 +5515,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>8.563785224144926</v>
       </c>
       <c r="C7" t="n">
-        <v>21.02020009562846</v>
+        <v>21.13997331554657</v>
       </c>
       <c r="D7" t="n">
         <v>39.52516257297658</v>
@@ -5529,10 +5529,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>10.84831213192725</v>
       </c>
       <c r="C8" t="n">
-        <v>31.46010518258904</v>
+        <v>31.62700229231099</v>
       </c>
       <c r="D8" t="n">
         <v>39.8884092235479</v>
@@ -5546,10 +5546,10 @@
         <v>10.6499990956694</v>
       </c>
       <c r="C9" t="n">
-        <v>33.72499713628642</v>
+        <v>33.9468721174462</v>
       </c>
       <c r="D9" t="n">
-        <v>42.3781214015178</v>
+        <v>42.15624642035802</v>
       </c>
     </row>
     <row r="10">
@@ -5563,7 +5563,7 @@
         <v>33.59540643932586</v>
       </c>
       <c r="D10" t="n">
-        <v>48.54251523648354</v>
+        <v>48.68486865359933</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>8.707120388964958</v>
       </c>
       <c r="C11" t="n">
-        <v>33.93999988351647</v>
+        <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
-        <v>50.6434553235717</v>
+        <v>50.82115165804038</v>
       </c>
     </row>
     <row r="12">
@@ -5602,7 +5602,7 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>33.04071898642641</v>
+        <v>33.30088212805181</v>
       </c>
       <c r="D13" t="n">
         <v>45.78871292607123</v>
@@ -5619,7 +5619,7 @@
         <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.02537087605695</v>
+        <v>28.66703296400686</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>43.71722527011046</v>
       </c>
     </row>
     <row r="16">
@@ -5644,7 +5644,7 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
         <v>41.74489413227862</v>
@@ -5658,7 +5658,7 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
         <v>36.83321036793183</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.04401628124632</v>
+        <v>18.04988324431451</v>
       </c>
       <c r="C21" t="n">
-        <v>117.7157252633689</v>
+        <v>117.7540002129089</v>
       </c>
       <c r="D21" t="n">
-        <v>6.014672093748773</v>
+        <v>6.016627748104836</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.508586368528853</v>
+        <v>5.373105185342792</v>
       </c>
       <c r="C2" t="n">
-        <v>6.547275439621979</v>
+        <v>5.876741757621406</v>
       </c>
       <c r="D2" t="n">
-        <v>32.75993914301181</v>
+        <v>25.2849121228766</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.92470852640926</v>
+        <v>13.94081740030471</v>
       </c>
       <c r="C3" t="n">
-        <v>30.42436135460865</v>
+        <v>25.67270246605409</v>
       </c>
       <c r="D3" t="n">
-        <v>63.51907646476863</v>
+        <v>48.39034434232529</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>19.62906359871073</v>
+        <v>21.56899706230242</v>
       </c>
       <c r="C4" t="n">
-        <v>54.38195058134357</v>
+        <v>54.07564529761856</v>
       </c>
       <c r="D4" t="n">
-        <v>57.20251173564466</v>
+        <v>43.18904500522568</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>17.79417713947344</v>
+        <v>19.9785657814226</v>
       </c>
       <c r="C5" t="n">
-        <v>63.37181430913162</v>
+        <v>68.32964021557801</v>
       </c>
       <c r="D5" t="n">
-        <v>37.45367491701582</v>
+        <v>32.07860623626453</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.42517887139688</v>
+        <v>11.5119735799981</v>
       </c>
       <c r="C6" t="n">
-        <v>49.50953672516665</v>
+        <v>54.37998708593508</v>
       </c>
       <c r="D6" t="n">
-        <v>32.32207966691774</v>
+        <v>31.35603992593888</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.030475236560656</v>
+        <v>5.150248456478767</v>
       </c>
       <c r="C7" t="n">
-        <v>23.35577788403162</v>
+        <v>27.5478405811655</v>
       </c>
       <c r="D7" t="n">
-        <v>30.84160412891355</v>
+        <v>30.78171751895449</v>
       </c>
     </row>
     <row r="8">
@@ -5843,7 +5843,7 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>18.44213062427633</v>
       </c>
       <c r="D8" t="n">
         <v>30.0414797499524</v>
@@ -5857,10 +5857,10 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>21.63281066307846</v>
+        <v>21.96562313481813</v>
       </c>
       <c r="D9" t="n">
-        <v>30.39687241888974</v>
+        <v>29.95312245657017</v>
       </c>
     </row>
     <row r="10">
@@ -5871,10 +5871,10 @@
         <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>21.49536598448391</v>
       </c>
       <c r="D10" t="n">
-        <v>33.02599277086271</v>
+        <v>33.45305302221006</v>
       </c>
     </row>
     <row r="11">
@@ -5885,7 +5885,7 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.43507846389736</v>
+        <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
         <v>34.65078522139116</v>
@@ -5899,10 +5899,10 @@
         <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>19.7439280801076</v>
       </c>
       <c r="D12" t="n">
-        <v>31.67707142522758</v>
+        <v>31.89403766786613</v>
       </c>
     </row>
     <row r="13">
@@ -5941,10 +5941,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
-        <v>27.95035713990669</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -6011,7 +6011,7 @@
         <v>1.34499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.08745766113597</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.048708421389251</v>
+        <v>7.052087602943849</v>
       </c>
       <c r="C21" t="n">
-        <v>66.08164145052423</v>
+        <v>66.11332127759857</v>
       </c>
       <c r="D21" t="n">
-        <v>4.405442763368281</v>
+        <v>4.407554751839905</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.437499623195583</v>
+        <v>4.683918296961532</v>
       </c>
       <c r="C2" t="n">
-        <v>5.546874528994478</v>
+        <v>5.446736263161304</v>
       </c>
       <c r="D2" t="n">
-        <v>40.11322944782042</v>
+        <v>25.76695024566178</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.73879835740812</v>
+        <v>16.87624303600267</v>
       </c>
       <c r="C3" t="n">
-        <v>27.3318560862312</v>
+        <v>23.92519155249477</v>
       </c>
       <c r="D3" t="n">
-        <v>75.68783925890784</v>
+        <v>57.93784076612551</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.24091340263474</v>
+        <v>25.05321966467436</v>
       </c>
       <c r="C4" t="n">
-        <v>67.96148482648545</v>
+        <v>60.61015801708533</v>
       </c>
       <c r="D4" t="n">
-        <v>77.21445693901164</v>
+        <v>58.10866486666446</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>24.44551783574558</v>
+        <v>27.41530464109218</v>
       </c>
       <c r="C5" t="n">
-        <v>85.78020565856507</v>
+        <v>87.76824475966485</v>
       </c>
       <c r="D5" t="n">
-        <v>49.87278337573798</v>
+        <v>41.35612204139689</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>18.31450342272425</v>
+        <v>20.44784118405257</v>
       </c>
       <c r="C6" t="n">
-        <v>78.69198723390311</v>
+        <v>86.38005350585986</v>
       </c>
       <c r="D6" t="n">
-        <v>37.43403996293088</v>
+        <v>34.97868895460962</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.282424543653592</v>
+        <v>10.00106386316226</v>
       </c>
       <c r="C7" t="n">
-        <v>51.44259795482861</v>
+        <v>57.31148573081605</v>
       </c>
       <c r="D7" t="n">
-        <v>33.41672835715293</v>
+        <v>33.11729530735765</v>
       </c>
     </row>
     <row r="8">
@@ -6151,10 +6151,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.340707511102648</v>
+        <v>5.507604620824606</v>
       </c>
       <c r="C8" t="n">
-        <v>26.03594911662541</v>
+        <v>28.95664853675967</v>
       </c>
       <c r="D8" t="n">
         <v>32.12769362147687</v>
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
-        <v>23.07499804061703</v>
+        <v>23.2968730217768</v>
       </c>
       <c r="D9" t="n">
-        <v>31.72812230584841</v>
+        <v>31.39530983410874</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>24.48478774391545</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>33.31069960509428</v>
+        <v>33.59540643932586</v>
       </c>
     </row>
     <row r="11">
@@ -6196,7 +6196,7 @@
         <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
         <v>35.36157055926586</v>
@@ -6213,7 +6213,7 @@
         <v>21.91359050649305</v>
       </c>
       <c r="D12" t="n">
-        <v>32.97886888105885</v>
+        <v>33.1958351236974</v>
       </c>
     </row>
     <row r="13">
@@ -6227,7 +6227,7 @@
         <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
-        <v>30.69925071179776</v>
+        <v>30.95941385342317</v>
       </c>
     </row>
     <row r="14">
@@ -6266,10 +6266,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>16.11931555602838</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -6297,7 +6297,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6311,7 +6311,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6322,7 +6322,7 @@
         <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.266334180773396</v>
+        <v>7.27239636843983</v>
       </c>
       <c r="C21" t="n">
-        <v>75.38821712552399</v>
+        <v>75.45111232256325</v>
       </c>
       <c r="D21" t="n">
-        <v>5.449750635580047</v>
+        <v>5.454297276329872</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.426299487821368</v>
+        <v>3.851396243760237</v>
       </c>
       <c r="C2" t="n">
-        <v>4.666246838285089</v>
+        <v>4.510148953309847</v>
       </c>
       <c r="D2" t="n">
-        <v>32.75699389989908</v>
+        <v>21.88021108454867</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.93376523992573</v>
+        <v>16.51299638543135</v>
       </c>
       <c r="C3" t="n">
-        <v>23.92519155249477</v>
+        <v>22.28076414788136</v>
       </c>
       <c r="D3" t="n">
-        <v>89.33904108645976</v>
+        <v>65.10950774564847</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.48639138642545</v>
+        <v>29.62227348023901</v>
       </c>
       <c r="C4" t="n">
-        <v>67.59136594198441</v>
+        <v>59.65295400544469</v>
       </c>
       <c r="D4" t="n">
-        <v>95.92460468654734</v>
+        <v>74.10035322114076</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29.91876128692155</v>
+        <v>32.96217917008666</v>
       </c>
       <c r="C5" t="n">
-        <v>108.1395096227862</v>
+        <v>101.6845184673634</v>
       </c>
       <c r="D5" t="n">
-        <v>66.34160111447822</v>
+        <v>52.52350217720437</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>26.28433128579986</v>
+        <v>29.66547037922588</v>
       </c>
       <c r="C6" t="n">
-        <v>109.9272721922196</v>
+        <v>115.7637622939669</v>
       </c>
       <c r="D6" t="n">
-        <v>44.19631814978292</v>
+        <v>40.45291415348983</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.75017841923158</v>
+        <v>17.6066633279623</v>
       </c>
       <c r="C7" t="n">
-        <v>84.32034682235003</v>
+        <v>94.26152407555324</v>
       </c>
       <c r="D7" t="n">
-        <v>36.9500383447372</v>
+        <v>36.11162580531042</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.927612711792993</v>
+        <v>8.511752595819845</v>
       </c>
       <c r="C8" t="n">
-        <v>48.81740459367264</v>
+        <v>54.07466354991431</v>
       </c>
       <c r="D8" t="n">
-        <v>33.88011327355743</v>
+        <v>33.79666471869644</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>5.546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>28.51093507903161</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>33.17030968338697</v>
+        <v>32.9484347022272</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>4.982369599052563</v>
       </c>
       <c r="C10" t="n">
-        <v>26.76244241776806</v>
+        <v>27.04714925199963</v>
       </c>
       <c r="D10" t="n">
-        <v>34.02246669067321</v>
+        <v>33.88011327355743</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>4.264712027248144</v>
       </c>
       <c r="C11" t="n">
-        <v>26.12136116689488</v>
+        <v>26.65445017030089</v>
       </c>
       <c r="D11" t="n">
-        <v>35.53926689373453</v>
+        <v>35.89465956267188</v>
       </c>
     </row>
     <row r="12">
@@ -6524,7 +6524,7 @@
         <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>34.06370009425158</v>
+        <v>34.28066633689012</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
         <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
-        <v>31.21957699504857</v>
+        <v>31.47974013667398</v>
       </c>
     </row>
     <row r="14">
@@ -6549,7 +6549,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.20280516861837</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
         <v>30.42141611149592</v>
@@ -6566,7 +6566,7 @@
         <v>19.35024725070463</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -6577,10 +6577,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>17.3592629064921</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -6608,7 +6608,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6633,7 +6633,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.469732589303343</v>
+        <v>7.479850884254936</v>
       </c>
       <c r="C21" t="n">
-        <v>84.03449162966261</v>
+        <v>84.14832244786803</v>
       </c>
       <c r="D21" t="n">
-        <v>6.536016015640425</v>
+        <v>6.544869523723069</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_88_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_88_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497635042322</v>
+        <v>10.84497654852724</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907200535541</v>
+        <v>37.78907269564434</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.661739010391356</v>
+        <v>1.372483290537041</v>
       </c>
       <c r="C2" t="n">
-        <v>5.625414345334224</v>
+        <v>2.484803439448677</v>
       </c>
       <c r="D2" t="n">
-        <v>26.78796785807847</v>
+        <v>19.61237388773853</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.66731070144735</v>
+        <v>11.11338401207389</v>
       </c>
       <c r="C3" t="n">
-        <v>19.58095796120263</v>
+        <v>33.04562772494764</v>
       </c>
       <c r="D3" t="n">
-        <v>67.00428081484482</v>
+        <v>75.43258485580367</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.59224021203486</v>
+        <v>17.1913840490659</v>
       </c>
       <c r="C4" t="n">
-        <v>57.50881701936967</v>
+        <v>105.5859838440402</v>
       </c>
       <c r="D4" t="n">
-        <v>87.57778570504097</v>
+        <v>83.05978277009714</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.99992755120455</v>
+        <v>15.38889526406876</v>
       </c>
       <c r="C5" t="n">
-        <v>105.0960917396211</v>
+        <v>108.9249077861836</v>
       </c>
       <c r="D5" t="n">
-        <v>66.46431957750907</v>
+        <v>51.36994862471437</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.11202671593793</v>
+        <v>10.86794708601219</v>
       </c>
       <c r="C6" t="n">
-        <v>139.4719876038232</v>
+        <v>69.07184147998861</v>
       </c>
       <c r="D6" t="n">
-        <v>46.93343074922303</v>
+        <v>29.78622534684823</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>26.58965482182061</v>
+        <v>6.048547605864599</v>
       </c>
       <c r="C7" t="n">
-        <v>130.732469540618</v>
+        <v>38.92629647338602</v>
       </c>
       <c r="D7" t="n">
-        <v>39.70482240285375</v>
+        <v>29.52409870981433</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.68556299720053</v>
+        <v>6.091744504851458</v>
       </c>
       <c r="C8" t="n">
-        <v>90.37478491444013</v>
+        <v>28.70630287217673</v>
       </c>
       <c r="D8" t="n">
-        <v>35.63253292563798</v>
+        <v>31.2097595180061</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.09999939711293</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>49.25624581747095</v>
+        <v>31.72812230584841</v>
       </c>
       <c r="D9" t="n">
-        <v>34.39062207976576</v>
+        <v>34.83437204208531</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.409429850399925</v>
+        <v>3.4164820107789</v>
       </c>
       <c r="C10" t="n">
-        <v>32.02951885105219</v>
+        <v>30.17892442854695</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>38.43542262126263</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>37.6716229073586</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>27.33774657245668</v>
+        <v>24.0832529328785</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>37.96909246174538</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>25.49598787928967</v>
+        <v>20.03256190515617</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>35.90251354430586</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>23.66110142005238</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>27.3485457972034</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>17.9443845382232</v>
+        <v>24.55547357862122</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>18.41660518396592</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>26.21757244191107</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>11.23610247510475</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>11.4344155113626</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>85.45721066386785</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.673749404804173</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>93.04421153325059</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.673749404804173</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.801548095021903</v>
+        <v>0.9375690575557039</v>
       </c>
       <c r="C2" t="n">
-        <v>8.927031874716247</v>
+        <v>6.007314202286233</v>
       </c>
       <c r="D2" t="n">
-        <v>27.81782119983337</v>
+        <v>17.41227728252143</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.65534980254714</v>
+        <v>7.69199326277376</v>
       </c>
       <c r="C3" t="n">
-        <v>20.64615422031042</v>
+        <v>19.40424337443821</v>
       </c>
       <c r="D3" t="n">
-        <v>71.60376880924112</v>
+        <v>73.55744674069227</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.95861203216817</v>
+        <v>19.66735175917635</v>
       </c>
       <c r="C4" t="n">
-        <v>53.14396672628834</v>
+        <v>93.64007777876502</v>
       </c>
       <c r="D4" t="n">
-        <v>99.05147112457344</v>
+        <v>101.1573199501829</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.01880174176349</v>
+        <v>20.64124548178919</v>
       </c>
       <c r="C5" t="n">
-        <v>104.4334120392545</v>
+        <v>155.4352052748763</v>
       </c>
       <c r="D5" t="n">
-        <v>79.44793296617314</v>
+        <v>68.52598975642738</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44.63908636439822</v>
+        <v>15.61764247915826</v>
       </c>
       <c r="C6" t="n">
-        <v>152.916040665779</v>
+        <v>123.6933385011684</v>
       </c>
       <c r="D6" t="n">
-        <v>55.82904669740338</v>
+        <v>38.23907308041327</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>34.55457394637499</v>
+        <v>9.222537933694536</v>
       </c>
       <c r="C7" t="n">
-        <v>163.2508987483851</v>
+        <v>69.94756043217674</v>
       </c>
       <c r="D7" t="n">
-        <v>43.29801900039708</v>
+        <v>31.50035683846316</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>20.5283444958008</v>
+        <v>6.592435834017332</v>
       </c>
       <c r="C8" t="n">
-        <v>129.8459513636831</v>
+        <v>40.47254910757476</v>
       </c>
       <c r="D8" t="n">
-        <v>38.13598957146735</v>
+        <v>32.62838495064274</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.20624913334984</v>
+        <v>6.212499472473814</v>
       </c>
       <c r="C9" t="n">
-        <v>77.87811838708245</v>
+        <v>34.94530953266521</v>
       </c>
       <c r="D9" t="n">
-        <v>35.38905949498476</v>
+        <v>35.27812200440487</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.121196935978863</v>
+        <v>4.128249096357838</v>
       </c>
       <c r="C10" t="n">
-        <v>44.4142661401257</v>
+        <v>34.73423377625215</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>39.14718970684157</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>33.05151821117311</v>
+        <v>34.47308888692249</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>38.56010457970196</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>30.37527396939631</v>
+        <v>28.8565102709265</v>
       </c>
       <c r="D12" t="n">
-        <v>35.79943003535993</v>
+        <v>38.40302494702248</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>27.57729301229291</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>36.68300296918207</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>25.81211064005714</v>
+        <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>28.88498095434966</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>25.44199175555609</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.66578917439536</v>
+        <v>25.62557857625024</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>21.49242074137117</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>17.47216389248049</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>9.095892479846698</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>50.82998738737861</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>9.095892479846698</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>46.33947338815369</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.852985073188992</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>101.1071828173083</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.834608207337617</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.463246047684253</v>
+        <v>0.4977460860531329</v>
       </c>
       <c r="C2" t="n">
-        <v>7.794095024015427</v>
+        <v>2.471058971589222</v>
       </c>
       <c r="D2" t="n">
-        <v>22.02550974477719</v>
+        <v>11.71323185936869</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.13426275577033</v>
+        <v>6.582618356974864</v>
       </c>
       <c r="C3" t="n">
-        <v>27.12568906833937</v>
+        <v>22.7618205229623</v>
       </c>
       <c r="D3" t="n">
-        <v>76.2278004962436</v>
+        <v>73.28255738350316</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.55845987946297</v>
+        <v>21.47965802121596</v>
       </c>
       <c r="C4" t="n">
-        <v>52.26333903557895</v>
+        <v>84.57854646856697</v>
       </c>
       <c r="D4" t="n">
-        <v>107.6280190688736</v>
+        <v>114.2773962697372</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.77965621255477</v>
+        <v>20.69033286700153</v>
       </c>
       <c r="C5" t="n">
-        <v>100.3100716814179</v>
+        <v>181.206082511355</v>
       </c>
       <c r="D5" t="n">
-        <v>92.23519681398784</v>
+        <v>77.16536955379931</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.46928506929254</v>
+        <v>12.7597749120958</v>
       </c>
       <c r="C6" t="n">
-        <v>159.1147956703933</v>
+        <v>160.5638552818616</v>
       </c>
       <c r="D6" t="n">
-        <v>65.81145735418494</v>
+        <v>38.84284791852506</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>42.22006002113408</v>
+        <v>4.311835917051991</v>
       </c>
       <c r="C7" t="n">
-        <v>187.3852025618845</v>
+        <v>68.21084874336412</v>
       </c>
       <c r="D7" t="n">
-        <v>47.84940135728529</v>
+        <v>33.35684174719388</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>27.53802310412303</v>
+        <v>4.255876297909922</v>
       </c>
       <c r="C8" t="n">
-        <v>166.7302126122358</v>
+        <v>39.97185777840888</v>
       </c>
       <c r="D8" t="n">
-        <v>40.72289477215769</v>
+        <v>36.21667280966483</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14.53281126596553</v>
+        <v>2.884374755077128</v>
       </c>
       <c r="C9" t="n">
-        <v>114.0437403161264</v>
+        <v>26.5140602485936</v>
       </c>
       <c r="D9" t="n">
-        <v>36.60937189136354</v>
+        <v>40.93593402397924</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.687084524252525</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>64.05903770210438</v>
+        <v>27.04714925199963</v>
       </c>
       <c r="D10" t="n">
-        <v>36.44247478164161</v>
+        <v>30.17892442854695</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.153193699591506</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>40.51476425885736</v>
+        <v>23.10052348092744</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>30.74146586308036</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>1.301797455831271</v>
       </c>
       <c r="C12" t="n">
-        <v>33.62976760897449</v>
+        <v>18.65909686691488</v>
       </c>
       <c r="D12" t="n">
-        <v>36.23336252063703</v>
+        <v>29.94134148411922</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>17.17076734727672</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>27.65583282863265</v>
+        <v>19.0517959486136</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>21.20280516861837</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>24.72531593145592</v>
+        <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>17.91689560250429</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>21.90573652485908</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>7.083309686140737</v>
       </c>
       <c r="C17" t="n">
-        <v>19.83326712119407</v>
+        <v>43.91652005407257</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>7.555530331883453</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>40.12893741108837</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.017249497790278</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>109.2350244073925</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10.02156187223785</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.792712365683681</v>
+        <v>0.9071348787240529</v>
       </c>
       <c r="C2" t="n">
-        <v>5.299474107524283</v>
+        <v>4.734969177582366</v>
       </c>
       <c r="D2" t="n">
-        <v>18.20552942755285</v>
+        <v>13.37631247036279</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.91260875878881</v>
+        <v>4.054618018539327</v>
       </c>
       <c r="C3" t="n">
-        <v>38.81830422591889</v>
+        <v>15.36435157146258</v>
       </c>
       <c r="D3" t="n">
-        <v>82.96749848589795</v>
+        <v>66.58703804053992</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>20.54797944988574</v>
+        <v>17.39558757154924</v>
       </c>
       <c r="C4" t="n">
-        <v>79.16715312275853</v>
+        <v>70.22048629395735</v>
       </c>
       <c r="D4" t="n">
-        <v>103.4035586974995</v>
+        <v>123.9770635876957</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.85709110800325</v>
+        <v>26.31083847381452</v>
       </c>
       <c r="C5" t="n">
-        <v>95.05772146369743</v>
+        <v>169.8914402199105</v>
       </c>
       <c r="D5" t="n">
-        <v>64.10812508731674</v>
+        <v>98.07659565425638</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>26.20382797405162</v>
+        <v>19.40129813132547</v>
       </c>
       <c r="C6" t="n">
-        <v>123.4115769100496</v>
+        <v>226.3350609801724</v>
       </c>
       <c r="D6" t="n">
-        <v>31.51704654943536</v>
+        <v>52.16614601285853</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.20552942755285</v>
+        <v>8.384125394267761</v>
       </c>
       <c r="C7" t="n">
-        <v>117.2579822998305</v>
+        <v>144.745936271037</v>
       </c>
       <c r="D7" t="n">
-        <v>28.62579956042849</v>
+        <v>36.35117224514665</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.09727513817844</v>
+        <v>4.589670517353839</v>
       </c>
       <c r="C8" t="n">
-        <v>84.03269474500573</v>
+        <v>62.83676181031709</v>
       </c>
       <c r="D8" t="n">
-        <v>26.95388322009618</v>
+        <v>37.46840113257952</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.435937038414587</v>
+        <v>3.328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>48.92343334573128</v>
+        <v>36.83124687252333</v>
       </c>
       <c r="D9" t="n">
-        <v>27.73437264497238</v>
+        <v>42.04530892977813</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.701188845010476</v>
+        <v>2.2776546738526</v>
       </c>
       <c r="C10" t="n">
-        <v>31.74481201682062</v>
+        <v>30.17892442854695</v>
       </c>
       <c r="D10" t="n">
-        <v>28.32833000604172</v>
+        <v>31.8871654339364</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>1.421570675749381</v>
       </c>
       <c r="C11" t="n">
         <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
-        <v>28.96450251839364</v>
+        <v>31.8076438698924</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>24.30021917551705</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>26.68684784454105</v>
+        <v>30.8092064546734</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.560978849752429</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>20.58823110575986</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>23.66110142005238</v>
+        <v>20.89551813718911</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.27523351455437</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>22.93362637120549</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>16.94594712300419</v>
+        <v>37.19842051391164</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>12.81278928812512</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.58328130950962</v>
+        <v>47.6942852200143</v>
       </c>
       <c r="D17" t="n">
-        <v>17.47216389248049</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>73.30219233758808</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.052654523130833</v>
+        <v>0.5556692006036947</v>
       </c>
       <c r="C2" t="n">
-        <v>2.949170103557418</v>
+        <v>2.426880324898115</v>
       </c>
       <c r="D2" t="n">
-        <v>14.06353586333556</v>
+        <v>10.76584532477052</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.18888077430966</v>
+        <v>3.696280106489241</v>
       </c>
       <c r="C3" t="n">
-        <v>30.0267535343887</v>
+        <v>17.3278469799562</v>
       </c>
       <c r="D3" t="n">
-        <v>79.28103585645118</v>
+        <v>62.78767442510475</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.62227348023901</v>
+        <v>13.96241584979814</v>
       </c>
       <c r="C4" t="n">
-        <v>90.79399118415351</v>
+        <v>56.81963013098839</v>
       </c>
       <c r="D4" t="n">
-        <v>119.4845860930623</v>
+        <v>130.1286947025062</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.53235360207581</v>
+        <v>27.85709110800325</v>
       </c>
       <c r="C5" t="n">
-        <v>121.2458414744811</v>
+        <v>158.4786231580414</v>
       </c>
       <c r="D5" t="n">
-        <v>80.18424374435826</v>
+        <v>113.5391219961436</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.35603992593888</v>
+        <v>23.98998690097506</v>
       </c>
       <c r="C6" t="n">
-        <v>140.9210472152914</v>
+        <v>254.2294585009371</v>
       </c>
       <c r="D6" t="n">
-        <v>39.1246095096439</v>
+        <v>64.52340436621313</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.12757044828985</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>145.7041220303819</v>
+        <v>211.0404134957113</v>
       </c>
       <c r="D7" t="n">
-        <v>31.26081039862693</v>
+        <v>40.12402867256714</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.511752595819845</v>
+        <v>4.339324852770902</v>
       </c>
       <c r="C8" t="n">
-        <v>108.7334669838555</v>
+        <v>97.46791207762332</v>
       </c>
       <c r="D8" t="n">
-        <v>28.12216298814988</v>
+        <v>40.3056519978528</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.548437113775471</v>
+        <v>2.884374755077128</v>
       </c>
       <c r="C9" t="n">
-        <v>55.69062027110455</v>
+        <v>47.59218345877262</v>
       </c>
       <c r="D9" t="n">
-        <v>28.6218725696115</v>
+        <v>42.04530892977813</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>33.88011327355743</v>
+        <v>32.88363935374691</v>
       </c>
       <c r="D10" t="n">
-        <v>29.75186417719959</v>
+        <v>32.88363935374691</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>29.31989518733098</v>
+        <v>27.54293184264426</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>33.05151821117311</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>21.04572553593887</v>
+        <v>22.99842171968578</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>29.50740899884213</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>16.91060420565131</v>
+        <v>17.43093048890212</v>
       </c>
       <c r="D13" t="n">
-        <v>24.97566159603886</v>
+        <v>24.19517217116264</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>16.59349969717959</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>14.33351648200343</v>
+        <v>31.53373626040754</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.75013736150257</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.22610507161303</v>
+        <v>40.5049467818149</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>63.79200232654924</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.765984193490764</v>
+        <v>0.6175193059712437</v>
       </c>
       <c r="C2" t="n">
-        <v>12.13440162449058</v>
+        <v>13.56088103876119</v>
       </c>
       <c r="D2" t="n">
-        <v>16.82322865997334</v>
+        <v>13.74839485027233</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.42740440871263</v>
+        <v>2.788163480060942</v>
       </c>
       <c r="C3" t="n">
-        <v>19.96874830438012</v>
+        <v>13.26341148437441</v>
       </c>
       <c r="D3" t="n">
-        <v>73.29237486054562</v>
+        <v>57.34879214357743</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.96083756948391</v>
+        <v>10.72068493037517</v>
       </c>
       <c r="C4" t="n">
-        <v>83.41713893444297</v>
+        <v>49.97881212779662</v>
       </c>
       <c r="D4" t="n">
-        <v>129.9883047807989</v>
+        <v>131.5708820800448</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.96280106489242</v>
+        <v>25.15728492132452</v>
       </c>
       <c r="C5" t="n">
-        <v>143.8014949795516</v>
+        <v>132.4868526881071</v>
       </c>
       <c r="D5" t="n">
-        <v>99.94191629232532</v>
+        <v>131.0633185169492</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.06548366321083</v>
+        <v>30.02773528209295</v>
       </c>
       <c r="C6" t="n">
-        <v>165.6355639220006</v>
+        <v>256.7653128210066</v>
       </c>
       <c r="D6" t="n">
-        <v>52.76992085097032</v>
+        <v>81.18758989809849</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.45180923259856</v>
+        <v>17.0676838383308</v>
       </c>
       <c r="C7" t="n">
-        <v>175.2282207401962</v>
+        <v>281.4071801976015</v>
       </c>
       <c r="D7" t="n">
-        <v>35.15344004596554</v>
+        <v>47.37030847761284</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.2669375645639</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>148.5384276525424</v>
+        <v>177.3281790795801</v>
       </c>
       <c r="D8" t="n">
-        <v>29.79113408536946</v>
+        <v>41.80772598535042</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.879687000734146</v>
+        <v>3.328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>90.63592980376974</v>
+        <v>78.5437433305618</v>
       </c>
       <c r="D9" t="n">
-        <v>29.28749751309084</v>
+        <v>42.93280885441725</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.704714925199962</v>
+        <v>1.70824100538945</v>
       </c>
       <c r="C10" t="n">
-        <v>46.97662764820988</v>
+        <v>43.13308538608361</v>
       </c>
       <c r="D10" t="n">
-        <v>30.46363126277853</v>
+        <v>35.01894061048373</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>34.11769621798515</v>
+        <v>32.16303653882975</v>
       </c>
       <c r="D11" t="n">
-        <v>30.20837685967435</v>
+        <v>33.40691088011046</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>25.16808414607123</v>
+        <v>26.25291535926396</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>30.15830772675777</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>20.03256190515617</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>24.97566159603886</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>16.59349969717959</v>
+        <v>20.58823110575986</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>16.90078672860884</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.866703296400686</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>31.89207417245764</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.46605242207675</v>
+        <v>41.33157834879071</v>
       </c>
       <c r="D16" t="n">
-        <v>14.46605242207675</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>11.33329549782518</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>34.9050578767911</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.235439522569987</v>
+        <v>0.414297531192154</v>
       </c>
       <c r="C2" t="n">
-        <v>5.557673753741193</v>
+        <v>7.159886007071988</v>
       </c>
       <c r="D2" t="n">
-        <v>11.62389281828223</v>
+        <v>9.897980354216342</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.86780821729195</v>
+        <v>3.926990816987242</v>
       </c>
       <c r="C3" t="n">
-        <v>33.33033455917921</v>
+        <v>29.01064466049325</v>
       </c>
       <c r="D3" t="n">
-        <v>72.74259614616741</v>
+        <v>62.97911522743289</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.75136545558085</v>
+        <v>17.35729941108361</v>
       </c>
       <c r="C4" t="n">
-        <v>79.90739089176064</v>
+        <v>71.45847014901258</v>
       </c>
       <c r="D4" t="n">
-        <v>139.8283620204647</v>
+        <v>135.0295792421063</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.68085954732433</v>
+        <v>18.53048791765855</v>
       </c>
       <c r="C5" t="n">
-        <v>168.5906245117835</v>
+        <v>207.9096200668683</v>
       </c>
       <c r="D5" t="n">
-        <v>105.6360529769568</v>
+        <v>120.1659189998096</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.43025184083414</v>
+        <v>10.58618549489336</v>
       </c>
       <c r="C6" t="n">
-        <v>204.7199217757704</v>
+        <v>248.2319617756933</v>
       </c>
       <c r="D6" t="n">
-        <v>51.80388110999145</v>
+        <v>67.86429180376503</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.084692344472483</v>
+        <v>4.311835917051991</v>
       </c>
       <c r="C7" t="n">
-        <v>187.8044088315978</v>
+        <v>124.6839219347534</v>
       </c>
       <c r="D7" t="n">
-        <v>35.03366682604743</v>
+        <v>36.35117224514665</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.005530633326986</v>
+        <v>2.253110981246429</v>
       </c>
       <c r="C8" t="n">
-        <v>113.3231375012093</v>
+        <v>57.82984851865836</v>
       </c>
       <c r="D8" t="n">
-        <v>31.46010518258904</v>
+        <v>31.62700229231099</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>1.220312396378785</v>
       </c>
       <c r="C9" t="n">
-        <v>35.83280945730432</v>
+        <v>32.8374972116473</v>
       </c>
       <c r="D9" t="n">
-        <v>31.8390597964283</v>
+        <v>26.73593522975338</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>26.76244241776806</v>
+        <v>25.19655482949439</v>
       </c>
       <c r="D10" t="n">
-        <v>23.63066724122073</v>
+        <v>26.1930287493049</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7107853378746906</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>20.07968579496001</v>
+        <v>20.96816746730337</v>
       </c>
       <c r="D11" t="n">
-        <v>23.10052348092744</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.62156946997525</v>
+        <v>16.27246819789088</v>
       </c>
       <c r="D12" t="n">
-        <v>21.04572553593887</v>
+        <v>20.39482680802324</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>13.52848336452105</v>
+        <v>16.91060420565131</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>13.78864650614645</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>26.73397173434489</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>8.604036880019047</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.18348900970292</v>
+        <v>35.1171153809084</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9.506263020221864</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29.27768003604838</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29.96293993361265</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.675663404700058</v>
+        <v>0.279798095710341</v>
       </c>
       <c r="C2" t="n">
-        <v>7.36212603414683</v>
+        <v>3.390956570468483</v>
       </c>
       <c r="D2" t="n">
-        <v>18.56386733960294</v>
+        <v>7.324819621385452</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.88543861823939</v>
+        <v>2.655627539987622</v>
       </c>
       <c r="C3" t="n">
-        <v>27.3318560862312</v>
+        <v>28.48050090019997</v>
       </c>
       <c r="D3" t="n">
-        <v>65.86545347791851</v>
+        <v>56.51921533348888</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.04566878267665</v>
+        <v>11.85656702418873</v>
       </c>
       <c r="C4" t="n">
-        <v>82.2429686801638</v>
+        <v>69.74826564821464</v>
       </c>
       <c r="D4" t="n">
-        <v>143.6188899065617</v>
+        <v>130.2946100645239</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.32653074154926</v>
+        <v>17.40147805777472</v>
       </c>
       <c r="C5" t="n">
-        <v>159.9512447144116</v>
+        <v>155.2143120414208</v>
       </c>
       <c r="D5" t="n">
-        <v>128.5107744859075</v>
+        <v>126.3509295365645</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.24536447726626</v>
+        <v>10.74719211838983</v>
       </c>
       <c r="C6" t="n">
-        <v>235.1501736166045</v>
+        <v>236.5187299163246</v>
       </c>
       <c r="D6" t="n">
-        <v>67.42152358914971</v>
+        <v>72.29197394991814</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.0676838383308</v>
+        <v>3.593196597543325</v>
       </c>
       <c r="C7" t="n">
-        <v>236.4323361183508</v>
+        <v>165.8260229766245</v>
       </c>
       <c r="D7" t="n">
-        <v>40.36357511240336</v>
+        <v>35.45287309576081</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.424156065963627</v>
+        <v>1.168279768053704</v>
       </c>
       <c r="C8" t="n">
-        <v>171.8205744587555</v>
+        <v>65.84090978531233</v>
       </c>
       <c r="D8" t="n">
-        <v>32.96217917008666</v>
+        <v>27.28767743954009</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>73.99530621678632</v>
+        <v>30.28593492830985</v>
       </c>
       <c r="D9" t="n">
-        <v>33.05937219280708</v>
+        <v>21.1890607007589</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>32.74128593663113</v>
+        <v>18.2212373908208</v>
       </c>
       <c r="D10" t="n">
-        <v>24.76949457814703</v>
+        <v>19.92947839621025</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.98900515327081</v>
+        <v>13.50492141961912</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>17.59193711239859</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.7912318963607</v>
+        <v>11.71617710248143</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>13.4519070435898</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>15.86995163914969</v>
+        <v>13.78864650614645</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>8.065057390387548</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.82791641431633</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>2.765583282863265</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.25850274585317</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>11.82515109765283</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.99988649347554</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.418044595559894</v>
+        <v>0.6499169802113884</v>
       </c>
       <c r="C2" t="n">
-        <v>3.984913931537803</v>
+        <v>4.808600255400877</v>
       </c>
       <c r="D2" t="n">
-        <v>13.10338660858218</v>
+        <v>14.58288039888212</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.86580366415445</v>
+        <v>1.73278469799562</v>
       </c>
       <c r="C3" t="n">
-        <v>28.20561154301086</v>
+        <v>19.35024725070463</v>
       </c>
       <c r="D3" t="n">
-        <v>65.51202430438966</v>
+        <v>49.80896977496192</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.7956829709922</v>
+        <v>8.308530821040756</v>
       </c>
       <c r="C4" t="n">
-        <v>78.27376271189394</v>
+        <v>71.35636838777093</v>
       </c>
       <c r="D4" t="n">
-        <v>144.3336022352533</v>
+        <v>128.1121849179833</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>53.16163818496479</v>
+        <v>18.06415775814131</v>
       </c>
       <c r="C5" t="n">
-        <v>162.1110896637546</v>
+        <v>140.831708174205</v>
       </c>
       <c r="D5" t="n">
-        <v>144.0714755982195</v>
+        <v>145.1513980728909</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>46.249152599363</v>
+        <v>17.10695374650067</v>
       </c>
       <c r="C6" t="n">
-        <v>253.3841737275806</v>
+        <v>245.3740942086308</v>
       </c>
       <c r="D6" t="n">
-        <v>80.30205346886787</v>
+        <v>94.59139130418019</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.92983824910874</v>
+        <v>7.845145904636261</v>
       </c>
       <c r="C7" t="n">
-        <v>280.3292212183385</v>
+        <v>256.9135567243478</v>
       </c>
       <c r="D7" t="n">
-        <v>45.75337000871835</v>
+        <v>47.07087542781757</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.506221962492859</v>
+        <v>2.336559536107409</v>
       </c>
       <c r="C8" t="n">
-        <v>213.7951975538279</v>
+        <v>144.1156542449105</v>
       </c>
       <c r="D8" t="n">
-        <v>34.04701038327938</v>
+        <v>30.70906818884022</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>0.6656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>85.97655519941439</v>
+        <v>55.80155776168444</v>
       </c>
       <c r="D9" t="n">
-        <v>32.8374972116473</v>
+        <v>22.96406055003713</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>33.59540643932586</v>
+        <v>27.04714925199963</v>
       </c>
       <c r="D10" t="n">
-        <v>25.19655482949439</v>
+        <v>20.64124548178919</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>17.05884810899257</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>18.30272245027328</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.57426565372215</v>
+        <v>13.4519070435898</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>14.10280577150543</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>11.44717823151781</v>
+        <v>14.04880964777186</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>8.585383673638358</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.06233313145306</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>3.072870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3481,10 +3481,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.219150722225291</v>
+        <v>0.7422012644105886</v>
       </c>
       <c r="C2" t="n">
-        <v>5.749114556069322</v>
+        <v>16.5728829953904</v>
       </c>
       <c r="D2" t="n">
-        <v>18.89275282052562</v>
+        <v>14.02426595516569</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.59305772882308</v>
+        <v>1.968404147014855</v>
       </c>
       <c r="C3" t="n">
-        <v>22.06477965294707</v>
+        <v>18.92318699935727</v>
       </c>
       <c r="D3" t="n">
-        <v>61.31505286873454</v>
+        <v>49.70588626601601</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.25215459573796</v>
+        <v>5.794274950464675</v>
       </c>
       <c r="C4" t="n">
-        <v>74.50876026610743</v>
+        <v>59.15520791939156</v>
       </c>
       <c r="D4" t="n">
-        <v>143.6827035073377</v>
+        <v>124.4492842334384</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52.71985171805373</v>
+        <v>15.70796326794897</v>
       </c>
       <c r="C5" t="n">
-        <v>153.9380400258999</v>
+        <v>136.1193191938203</v>
       </c>
       <c r="D5" t="n">
-        <v>156.2451471308799</v>
+        <v>155.8524480491812</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>55.30577517103983</v>
+        <v>20.56859615167493</v>
       </c>
       <c r="C6" t="n">
-        <v>256.0810346711465</v>
+        <v>236.0759617017093</v>
       </c>
       <c r="D6" t="n">
-        <v>100.1863714706828</v>
+        <v>116.6895503790716</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>29.46421209985527</v>
+        <v>13.71403368062369</v>
       </c>
       <c r="C7" t="n">
-        <v>319.854383791315</v>
+        <v>306.6194429903638</v>
       </c>
       <c r="D7" t="n">
-        <v>54.67647489261761</v>
+        <v>61.26400198811371</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.344855486097888</v>
+        <v>5.090361846519712</v>
       </c>
       <c r="C8" t="n">
-        <v>276.0478194801181</v>
+        <v>238.3290726829557</v>
       </c>
       <c r="D8" t="n">
-        <v>37.1346069131356</v>
+        <v>35.21529015133309</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.551562283337459</v>
+        <v>1.331249886958674</v>
       </c>
       <c r="C9" t="n">
-        <v>152.7609245285079</v>
+        <v>112.3796779574281</v>
       </c>
       <c r="D9" t="n">
-        <v>34.05780960802609</v>
+        <v>25.29374785221481</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7117670855789376</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>57.08372026343079</v>
+        <v>45.26838664282043</v>
       </c>
       <c r="D10" t="n">
-        <v>26.33538216642069</v>
+        <v>21.6377194015997</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>28.96450251839364</v>
+        <v>23.63361248433346</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>19.01350778814797</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>20.39482680802324</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>14.75370449942107</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.52848336452105</v>
+        <v>14.56913593102267</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>9.365873098514571</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.67690719431156</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>11.36962016288231</v>
+        <v>3.68744437715102</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>8.241771977151972</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.10547327717769</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.706498494159209</v>
+        <v>3.841578766717769</v>
       </c>
       <c r="C2" t="n">
-        <v>10.97692108118359</v>
+        <v>7.644869372969912</v>
       </c>
       <c r="D2" t="n">
-        <v>10.82573193472958</v>
+        <v>8.839656329038281</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.30219836645877</v>
+        <v>0.724529805734146</v>
       </c>
       <c r="C2" t="n">
-        <v>3.265292864324891</v>
+        <v>10.27988021116835</v>
       </c>
       <c r="D2" t="n">
-        <v>13.90547448295182</v>
+        <v>13.81417194645687</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.98499604699582</v>
+        <v>2.189297380470387</v>
       </c>
       <c r="C3" t="n">
-        <v>25.52053157189584</v>
+        <v>41.26285600949345</v>
       </c>
       <c r="D3" t="n">
-        <v>68.6192557883308</v>
+        <v>49.05793278121311</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.26638208968293</v>
+        <v>4.79878277835841</v>
       </c>
       <c r="C4" t="n">
-        <v>102.1655748424443</v>
+        <v>53.33540752861647</v>
       </c>
       <c r="D4" t="n">
-        <v>147.7667739570044</v>
+        <v>120.199298421754</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.61856747360028</v>
+        <v>12.73817646260237</v>
       </c>
       <c r="C5" t="n">
-        <v>222.9058162492383</v>
+        <v>123.4056864238241</v>
       </c>
       <c r="D5" t="n">
-        <v>142.427048193606</v>
+        <v>163.9273229166112</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>18.27425176685013</v>
+        <v>21.1321193339126</v>
       </c>
       <c r="C6" t="n">
-        <v>260.8709817201668</v>
+        <v>226.1338027008019</v>
       </c>
       <c r="D6" t="n">
-        <v>80.42280843649023</v>
+        <v>133.9977624049429</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.509568116233099</v>
+        <v>18.20552942755285</v>
       </c>
       <c r="C7" t="n">
-        <v>194.0925028772986</v>
+        <v>325.24417868763</v>
       </c>
       <c r="D7" t="n">
-        <v>33.0574086973986</v>
+        <v>77.13395362726339</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.752419652080557</v>
+        <v>9.179341034707678</v>
       </c>
       <c r="C8" t="n">
-        <v>112.5721005074605</v>
+        <v>311.7638009606171</v>
       </c>
       <c r="D8" t="n">
-        <v>25.03456645829366</v>
+        <v>41.72427743048944</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4437499623195582</v>
+        <v>2.773437264497239</v>
       </c>
       <c r="C9" t="n">
-        <v>43.4874963073167</v>
+        <v>192.4765461561084</v>
       </c>
       <c r="D9" t="n">
-        <v>20.07968579496001</v>
+        <v>27.5124976638126</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>22.63419332141022</v>
+        <v>81.99556825869361</v>
       </c>
       <c r="D10" t="n">
-        <v>19.21771131063132</v>
+        <v>22.776546738526</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>16.34806277111788</v>
+        <v>34.82848155585983</v>
       </c>
       <c r="D11" t="n">
-        <v>16.17036643664921</v>
+        <v>19.54659679155399</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.84831213192725</v>
+        <v>20.39482680802324</v>
       </c>
       <c r="D12" t="n">
-        <v>13.23494080095125</v>
+        <v>15.4046032273367</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.626036240139976</v>
+        <v>15.86995163914969</v>
       </c>
       <c r="D13" t="n">
-        <v>9.365873098514571</v>
+        <v>10.14636252339079</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.90078672860884</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>4.302018440009523</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>23.65030219530566</v>
+        <v>11.46681318560274</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>0.3583379120500857</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.708282063118455</v>
+        <v>4.429645641561608</v>
       </c>
       <c r="C2" t="n">
-        <v>4.978442608235575</v>
+        <v>8.56869396266616</v>
       </c>
       <c r="D2" t="n">
-        <v>20.16313434982099</v>
+        <v>23.91439232774806</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.004009106275</v>
+        <v>6.351907646476864</v>
       </c>
       <c r="C3" t="n">
-        <v>27.66074156715388</v>
+        <v>15.09437095279471</v>
       </c>
       <c r="D3" t="n">
-        <v>12.22766765639402</v>
+        <v>9.071348787240529</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>3.632466505713199</v>
       </c>
       <c r="C5" t="n">
-        <v>9.35114688295087</v>
+        <v>8.197593330460869</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>5.75598678999905</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>14.49059611468292</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.19040230136165</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.49536598448391</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>46.12250714551515</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.92282714645877</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.3974514252656</v>
+        <v>11.67837679977585</v>
       </c>
       <c r="C21" t="n">
-        <v>70.13959863815519</v>
+        <v>59.94900090551602</v>
       </c>
       <c r="D21" t="n">
-        <v>1.5761707559136</v>
+        <v>0.7785584533183899</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.233296100712247</v>
+        <v>2.408227118517426</v>
       </c>
       <c r="C2" t="n">
-        <v>7.323837873681205</v>
+        <v>5.548838024402973</v>
       </c>
       <c r="D2" t="n">
-        <v>16.34119053718816</v>
+        <v>24.04398302470863</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.85799074024948</v>
+        <v>12.05586180815083</v>
       </c>
       <c r="C3" t="n">
-        <v>22.50165738133689</v>
+        <v>27.34658230179491</v>
       </c>
       <c r="D3" t="n">
-        <v>26.20775496486861</v>
+        <v>27.83254741539707</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>11.72893982263664</v>
+        <v>7.963937376850126</v>
       </c>
       <c r="C4" t="n">
-        <v>42.69129891917255</v>
+        <v>25.09150782513998</v>
       </c>
       <c r="D4" t="n">
-        <v>21.47965802121596</v>
+        <v>18.96540215063988</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>2.454369260617026</v>
       </c>
       <c r="C5" t="n">
-        <v>5.473243451175969</v>
+        <v>5.056000676871074</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>25.72178985126644</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>5.433973543006096</v>
       </c>
       <c r="C6" t="n">
-        <v>16.34217228489241</v>
+        <v>13.68556299720054</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>30.06798693796707</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>6.827073535332318</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.58292145661112</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>6.926230053461247</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>20.36144738607885</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>20.85624822901923</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>22.776546738526</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>24.6997904911455</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.57268737340794</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>40.32528695193774</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43806771707706</v>
+        <v>13.629134795112</v>
       </c>
       <c r="C21" t="n">
-        <v>86.12816726369309</v>
+        <v>73.75767065590023</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250119519384645</v>
+        <v>1.603427622954353</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.66919208139783</v>
+        <v>1.920298509506761</v>
       </c>
       <c r="C2" t="n">
-        <v>7.637997139040184</v>
+        <v>3.926990816987241</v>
       </c>
       <c r="D2" t="n">
-        <v>17.88646142367264</v>
+        <v>25.70706363570273</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.05648370295658</v>
+        <v>9.935286766977722</v>
       </c>
       <c r="C3" t="n">
-        <v>26.13903262557133</v>
+        <v>23.73375075016664</v>
       </c>
       <c r="D3" t="n">
-        <v>33.19779861910589</v>
+        <v>41.30212591766332</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.6703380600181</v>
+        <v>17.26796036999714</v>
       </c>
       <c r="C4" t="n">
-        <v>50.75733805726435</v>
+        <v>51.94427103169874</v>
       </c>
       <c r="D4" t="n">
-        <v>29.77542612210151</v>
+        <v>29.15005283449629</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>10.55378782065321</v>
+        <v>7.682175785731292</v>
       </c>
       <c r="C5" t="n">
-        <v>47.27115195948392</v>
+        <v>29.82058651649687</v>
       </c>
       <c r="D5" t="n">
-        <v>30.38509144643879</v>
+        <v>26.75262494072559</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.957245069369646</v>
+        <v>4.427682146153116</v>
       </c>
       <c r="C6" t="n">
-        <v>12.23650338573225</v>
+        <v>10.50568218314512</v>
       </c>
       <c r="D6" t="n">
-        <v>36.54850353370026</v>
+        <v>31.95981476405067</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>6.94684675525043</v>
       </c>
       <c r="C7" t="n">
-        <v>24.13430381349934</v>
+        <v>20.00212772632452</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>32.81786225756237</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>7.593818492349078</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>23.94973524510094</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>33.96356182841841</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>7.432811868852599</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>23.96249796525614</v>
       </c>
       <c r="D9" t="n">
-        <v>41.15780900513902</v>
+        <v>36.49843440078366</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>24.62714116103124</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.69897297435728</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.174031385558941</v>
+        <v>6.397068040872215</v>
       </c>
       <c r="C11" t="n">
-        <v>30.91916219754903</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>44.42408361716816</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>31.89403766786613</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>42.09145107187774</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>41.10577637681396</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.23368131580652</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.72855287651986</v>
+        <v>14.83944006066852</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0441725467712</v>
+        <v>87.38781369060348</v>
       </c>
       <c r="D21" t="n">
-        <v>4.182138219129966</v>
+        <v>2.473240010111419</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.50327671938012</v>
+        <v>2.108794068722149</v>
       </c>
       <c r="C2" t="n">
-        <v>6.893832379221102</v>
+        <v>9.627017987844223</v>
       </c>
       <c r="D2" t="n">
-        <v>27.36523550817559</v>
+        <v>20.91908008209104</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.97794388661684</v>
+        <v>8.069966128908781</v>
       </c>
       <c r="C3" t="n">
-        <v>28.14670668075605</v>
+        <v>18.76610736667778</v>
       </c>
       <c r="D3" t="n">
-        <v>39.40735284846697</v>
+        <v>52.28297398966389</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.91206897944107</v>
+        <v>18.64633414675967</v>
       </c>
       <c r="C4" t="n">
-        <v>58.93824167675302</v>
+        <v>55.88795155965818</v>
       </c>
       <c r="D4" t="n">
-        <v>39.1815508764902</v>
+        <v>43.27838404631214</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>23.73375075016664</v>
+        <v>17.40147805777472</v>
       </c>
       <c r="C5" t="n">
-        <v>72.3793494955961</v>
+        <v>68.20692175254716</v>
       </c>
       <c r="D5" t="n">
-        <v>33.79666471869646</v>
+        <v>31.02322745419922</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.06291396852981</v>
+        <v>7.567311304334416</v>
       </c>
       <c r="C6" t="n">
-        <v>44.55858305264999</v>
+        <v>30.99377502307181</v>
       </c>
       <c r="D6" t="n">
-        <v>38.31957639216151</v>
+        <v>33.65038431076368</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.563785224144926</v>
+        <v>6.347980655659875</v>
       </c>
       <c r="C7" t="n">
-        <v>21.13997331554657</v>
+        <v>17.66654993792135</v>
       </c>
       <c r="D7" t="n">
-        <v>39.52516257297658</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>7.927612711792993</v>
       </c>
       <c r="C8" t="n">
-        <v>31.62700229231099</v>
+        <v>25.86905200690345</v>
       </c>
       <c r="D8" t="n">
-        <v>39.8884092235479</v>
+        <v>35.63253292563798</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>7.876561831172157</v>
       </c>
       <c r="C9" t="n">
-        <v>33.9468721174462</v>
+        <v>27.73437264497238</v>
       </c>
       <c r="D9" t="n">
-        <v>42.15624642035802</v>
+        <v>37.49687181600267</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>7.544731107136738</v>
       </c>
       <c r="C10" t="n">
-        <v>33.59540643932586</v>
+        <v>27.47420950334699</v>
       </c>
       <c r="D10" t="n">
-        <v>48.68486865359933</v>
+        <v>44.12955930589413</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.707120388964958</v>
+        <v>6.75246070980956</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>28.25371718051895</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>45.66795795844887</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>33.84673385161303</v>
+        <v>29.07347651356504</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>43.39324852770902</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>28.09761929554372</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>41.36593951843936</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>28.66703296400686</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>41.74489413227862</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.04988324431451</v>
+        <v>16.08225173904163</v>
       </c>
       <c r="C21" t="n">
-        <v>117.7540002129089</v>
+        <v>101.5721162465787</v>
       </c>
       <c r="D21" t="n">
-        <v>6.016627748104836</v>
+        <v>3.38573720821929</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.373105185342792</v>
+        <v>3.567671157232909</v>
       </c>
       <c r="C2" t="n">
-        <v>5.876741757621406</v>
+        <v>9.351146882950868</v>
       </c>
       <c r="D2" t="n">
-        <v>25.2849121228766</v>
+        <v>21.31374265919825</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.94081740030471</v>
+        <v>7.608544707912781</v>
       </c>
       <c r="C3" t="n">
-        <v>25.67270246605409</v>
+        <v>29.48679229705295</v>
       </c>
       <c r="D3" t="n">
-        <v>48.39034434232529</v>
+        <v>56.55357650313752</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.56899706230242</v>
+        <v>17.12757044828985</v>
       </c>
       <c r="C4" t="n">
-        <v>54.07564529761856</v>
+        <v>50.36169373245288</v>
       </c>
       <c r="D4" t="n">
-        <v>43.18904500522568</v>
+        <v>58.86166535582176</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>19.9785657814226</v>
+        <v>22.75200304591983</v>
       </c>
       <c r="C5" t="n">
-        <v>68.32964021557801</v>
+        <v>87.49826414099698</v>
       </c>
       <c r="D5" t="n">
-        <v>32.07860623626453</v>
+        <v>38.77903431774902</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.5119735799981</v>
+        <v>15.65789413503238</v>
       </c>
       <c r="C6" t="n">
-        <v>54.37998708593508</v>
+        <v>71.76870242355459</v>
       </c>
       <c r="D6" t="n">
-        <v>31.35603992593888</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.150248456478767</v>
+        <v>7.785259294677205</v>
       </c>
       <c r="C7" t="n">
-        <v>27.5478405811655</v>
+        <v>31.85967649821749</v>
       </c>
       <c r="D7" t="n">
-        <v>30.78171751895449</v>
+        <v>36.59071868498287</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>7.760715602071035</v>
       </c>
       <c r="C8" t="n">
-        <v>18.44213062427633</v>
+        <v>25.20146356801562</v>
       </c>
       <c r="D8" t="n">
-        <v>30.0414797499524</v>
+        <v>37.38495257771854</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>8.320311793491715</v>
       </c>
       <c r="C9" t="n">
-        <v>21.96562313481813</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>29.95312245657017</v>
+        <v>38.60624672180155</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>7.829437941368314</v>
       </c>
       <c r="C10" t="n">
-        <v>21.49536598448391</v>
+        <v>30.7483380970101</v>
       </c>
       <c r="D10" t="n">
-        <v>33.45305302221006</v>
+        <v>43.70249905454677</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>7.107853378746905</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>30.74146586308036</v>
       </c>
       <c r="D11" t="n">
-        <v>34.65078522139116</v>
+        <v>46.55643963079223</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>31.24313893995049</v>
       </c>
       <c r="D12" t="n">
-        <v>31.89403766786613</v>
+        <v>44.47807974090174</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>30.69925071179776</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>41.88626580169016</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>28.88498095434966</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>42.09832330580748</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>27.27884171020187</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>24.07245370813179</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.052087602943849</v>
+        <v>17.35191780469667</v>
       </c>
       <c r="C21" t="n">
-        <v>66.11332127759857</v>
+        <v>115.3902534012329</v>
       </c>
       <c r="D21" t="n">
-        <v>4.407554751839905</v>
+        <v>4.337979451174168</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.683918296961532</v>
+        <v>2.998257488769759</v>
       </c>
       <c r="C2" t="n">
-        <v>5.446736263161304</v>
+        <v>8.382161898859268</v>
       </c>
       <c r="D2" t="n">
-        <v>25.76695024566178</v>
+        <v>35.33800861436394</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.87624303600267</v>
+        <v>9.905834335850317</v>
       </c>
       <c r="C3" t="n">
-        <v>23.92519155249477</v>
+        <v>33.12416754128738</v>
       </c>
       <c r="D3" t="n">
-        <v>57.93784076612551</v>
+        <v>59.86206626644926</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.05321966467436</v>
+        <v>15.72367123121692</v>
       </c>
       <c r="C4" t="n">
-        <v>60.61015801708533</v>
+        <v>62.69048140238433</v>
       </c>
       <c r="D4" t="n">
-        <v>58.10866486666446</v>
+        <v>72.30080967925635</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.41530464109218</v>
+        <v>24.47006152835176</v>
       </c>
       <c r="C5" t="n">
-        <v>87.76824475966485</v>
+        <v>89.41267216427826</v>
       </c>
       <c r="D5" t="n">
-        <v>41.35612204139689</v>
+        <v>49.3573658310084</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>20.44784118405257</v>
+        <v>22.78243722475149</v>
       </c>
       <c r="C6" t="n">
-        <v>86.38005350585986</v>
+        <v>105.4190867343183</v>
       </c>
       <c r="D6" t="n">
-        <v>34.97868895460962</v>
+        <v>40.13090090649688</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.00106386316226</v>
+        <v>13.05528097107408</v>
       </c>
       <c r="C7" t="n">
-        <v>57.31148573081605</v>
+        <v>67.07300315414209</v>
       </c>
       <c r="D7" t="n">
-        <v>33.11729530735765</v>
+        <v>38.50709020367265</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.507604620824606</v>
+        <v>8.261406931236909</v>
       </c>
       <c r="C8" t="n">
-        <v>28.95664853675967</v>
+        <v>33.79666471869644</v>
       </c>
       <c r="D8" t="n">
-        <v>32.12769362147687</v>
+        <v>39.05392367493811</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>8.431249284071605</v>
       </c>
       <c r="C9" t="n">
-        <v>23.2968730217768</v>
+        <v>31.50624732468863</v>
       </c>
       <c r="D9" t="n">
-        <v>31.39530983410874</v>
+        <v>39.82655911818034</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>8.114144775599888</v>
       </c>
       <c r="C10" t="n">
-        <v>24.76949457814703</v>
+        <v>34.30717352490479</v>
       </c>
       <c r="D10" t="n">
-        <v>33.59540643932586</v>
+        <v>43.56014563743098</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>33.7623035490478</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>47.08952863419825</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>6.292021036517808</v>
       </c>
       <c r="C12" t="n">
-        <v>21.91359050649305</v>
+        <v>33.1958351236974</v>
       </c>
       <c r="D12" t="n">
-        <v>33.1958351236974</v>
+        <v>45.12897846881738</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>21.07321447165778</v>
+        <v>33.04071898642641</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>42.66675522656638</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.35908298004286</v>
+        <v>31.34327720578367</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>42.40561033723673</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.11931555602838</v>
+        <v>28.10547327717769</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>38.43836786437537</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>24.67426505083508</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>35.64235040268044</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.27239636843983</v>
+        <v>18.64167365377874</v>
       </c>
       <c r="C21" t="n">
-        <v>75.45111232256325</v>
+        <v>128.7163180856151</v>
       </c>
       <c r="D21" t="n">
-        <v>5.454297276329872</v>
+        <v>5.32619247250821</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.851396243760237</v>
+        <v>2.718459393059418</v>
       </c>
       <c r="C2" t="n">
-        <v>4.510148953309847</v>
+        <v>5.163011176633976</v>
       </c>
       <c r="D2" t="n">
-        <v>21.88021108454867</v>
+        <v>27.65190583781566</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.51299638543135</v>
+        <v>11.98713946885356</v>
       </c>
       <c r="C3" t="n">
-        <v>22.28076414788136</v>
+        <v>47.60985491744907</v>
       </c>
       <c r="D3" t="n">
-        <v>65.10950774564847</v>
+        <v>68.3001877844506</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.62227348023901</v>
+        <v>11.75446526294706</v>
       </c>
       <c r="C4" t="n">
-        <v>59.65295400544469</v>
+        <v>83.7489696584784</v>
       </c>
       <c r="D4" t="n">
-        <v>74.10035322114076</v>
+        <v>66.27680576599792</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.96217917008666</v>
+        <v>12.81180754042088</v>
       </c>
       <c r="C5" t="n">
-        <v>101.6845184673634</v>
+        <v>62.9791152274329</v>
       </c>
       <c r="D5" t="n">
-        <v>52.52350217720437</v>
+        <v>38.65631585471817</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.66547037922588</v>
+        <v>8.090582830697967</v>
       </c>
       <c r="C6" t="n">
-        <v>115.7637622939669</v>
+        <v>44.1560664939088</v>
       </c>
       <c r="D6" t="n">
-        <v>40.45291415348983</v>
+        <v>25.35854320069512</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.6066633279623</v>
+        <v>5.449681506274044</v>
       </c>
       <c r="C7" t="n">
-        <v>94.26152407555324</v>
+        <v>23.71509754378595</v>
       </c>
       <c r="D7" t="n">
-        <v>36.11162580531042</v>
+        <v>27.42806736124739</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.511752595819845</v>
+        <v>5.841398840268521</v>
       </c>
       <c r="C8" t="n">
-        <v>54.07466354991431</v>
+        <v>23.19869825135213</v>
       </c>
       <c r="D8" t="n">
-        <v>33.79666471869644</v>
+        <v>29.29044275620359</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.546874528994477</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>30.7296848906294</v>
+        <v>26.18124777685393</v>
       </c>
       <c r="D9" t="n">
-        <v>32.9484347022272</v>
+        <v>33.17030968338697</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>26.47773558353648</v>
       </c>
       <c r="D10" t="n">
-        <v>33.88011327355743</v>
+        <v>36.86953503298896</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.264712027248144</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>26.65445017030089</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.71459882216721</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>25.75615102091507</v>
       </c>
       <c r="D13" t="n">
-        <v>31.47974013667398</v>
+        <v>35.12202411942965</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>21.51009220004762</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>33.80157345721769</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>32.6087499965578</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>30.58536797810513</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>25.97213551584937</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>30.69237847786803</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>13.23984953947248</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>14.12244072559037</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>97.51209072431442</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.479850884254936</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>84.14832244786803</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>6.544869523723069</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
